--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyVariantAbility" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyVariantAbility" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyVariantAbility</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>98fabf8d61f37dd4</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>variant_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>ability_id</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyAbility.id&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,106 +407,859 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyVariantAbility</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>98fabf8d61f37dd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ability_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ability_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyVariant.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyAbility.id&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11025</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D9" t="n">
+        <v>11023</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D10" t="n">
+        <v>11024</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D11" t="n">
+        <v>11022</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D12" t="n">
+        <v>11026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>101</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11027</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>101</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>102</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11030</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11029</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>103</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11031</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>104</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11032</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>105</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11038</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>105</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11033</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>105</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11039</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>105</v>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>105</v>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11046</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>105</v>
+      </c>
+      <c r="C24" t="n">
+        <v>14</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11037</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>105</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11041</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>105</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11043</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>105</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11034</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>105</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11035</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>105</v>
+      </c>
+      <c r="C29" t="n">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="D29" t="n">
+        <v>11044</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>105</v>
+      </c>
+      <c r="C30" t="n">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="D30" t="n">
+        <v>11045</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>105</v>
+      </c>
+      <c r="C31" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="D31" t="n">
+        <v>11042</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>105</v>
+      </c>
+      <c r="C32" t="n">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D32" t="n">
+        <v>11036</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11047</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>107</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11048</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>107</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11050</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>107</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11049</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>108</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11052</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>108</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11053</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>108</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>11051</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>109</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11055</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>109</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11054</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>110</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11057</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>110</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11058</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>110</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>11056</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>111</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>11062</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>111</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>11060</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>111</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11063</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>111</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11061</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>111</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>11059</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>95</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>95</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>96</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>96</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>11003</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>96</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>11006</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>96</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>11004</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>97</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>11008</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>97</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>11011</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>97</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>11009</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>97</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>11007</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>97</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>11010</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>98</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>11012</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>98</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>11019</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>98</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11017</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>98</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11016</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>98</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>98</v>
+      </c>
+      <c r="C66" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+      <c r="D66" t="n">
+        <v>11020</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>98</v>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>11018</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>98</v>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>11015</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>98</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>11013</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>99</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11021</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,160 @@
         <v>11021</v>
       </c>
     </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>980101</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>980102</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>980103</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>980104</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>980105</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="n">
+        <v>980106</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>980107</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>980108</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C79" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" t="n">
+        <v>980109</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" t="n">
+        <v>980110</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+      <c r="D81" t="n">
+        <v>980111</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C82" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" t="n">
+        <v>980112</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>13</v>
+      </c>
+      <c r="D83" t="n">
+        <v>980113</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>14</v>
+      </c>
+      <c r="D84" t="n">
+        <v>980114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,6 +1416,94 @@
         <v>980114</v>
       </c>
     </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>990101</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>990102</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>990103</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="n">
+        <v>990104</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>990105</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" t="n">
+        <v>990106</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+      <c r="D91" t="n">
+        <v>990107</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>990108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,83 @@
         <v>990108</v>
       </c>
     </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1000101</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1000102</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1000103</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1000104</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1000105</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C98" t="n">
+        <v>6</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1000106</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1000109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,6 +1581,50 @@
         <v>1000109</v>
       </c>
     </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1010101</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1010102</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1010103</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1010104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1625,6 +1625,105 @@
         <v>1010104</v>
       </c>
     </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1020101</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1020102</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1020103</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1020104</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1020105</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C109" t="n">
+        <v>6</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1020106</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C110" t="n">
+        <v>7</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1020107</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C111" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1020108</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C112" t="n">
+        <v>9</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1020109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,6 +1724,94 @@
         <v>1020109</v>
       </c>
     </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1030101</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1030102</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1030103</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1030104</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1030105</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C118" t="n">
+        <v>6</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1030106</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C119" t="n">
+        <v>7</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1030108</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C120" t="n">
+        <v>8</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1030109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,6 +1812,116 @@
         <v>1030109</v>
       </c>
     </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1040101</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1040102</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1040103</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1040104</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1040105</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1040106</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C127" t="n">
+        <v>7</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1040107</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1040108</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C129" t="n">
+        <v>9</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1040112</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>10</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1040113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,6 +1922,50 @@
         <v>1040113</v>
       </c>
     </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1050101</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1050102</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1050103</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1050104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1966,6 +1966,105 @@
         <v>1050104</v>
       </c>
     </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1060101</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1060102</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1060103</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1060104</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C139" t="n">
+        <v>5</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1060105</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C140" t="n">
+        <v>6</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1060106</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C141" t="n">
+        <v>7</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1060107</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1060108</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C143" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1060109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,6 +2065,116 @@
         <v>1060109</v>
       </c>
     </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1070101</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1070102</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1070103</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C147" t="n">
+        <v>4</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1070104</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C148" t="n">
+        <v>5</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1070105</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C149" t="n">
+        <v>6</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1070106</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C150" t="n">
+        <v>7</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1070107</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1070108</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C152" t="n">
+        <v>9</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1070109</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C153" t="n">
+        <v>10</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1070110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2175,6 +2175,83 @@
         <v>1070110</v>
       </c>
     </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1080101</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1080102</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1080103</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C157" t="n">
+        <v>4</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1080104</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1080105</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C159" t="n">
+        <v>6</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1080106</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C160" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1080107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:J188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,123 +1033,123 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>11001</v>
+        <v>11008</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>11002</v>
+        <v>11011</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>11005</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>11003</v>
+        <v>11007</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>11006</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>11004</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>11008</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>11011</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>11009</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>11007</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>11010</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="61">
@@ -1157,10 +1157,10 @@
         <v>98</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>11012</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="62">
@@ -1168,10 +1168,10 @@
         <v>98</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>11019</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="63">
@@ -1179,87 +1179,87 @@
         <v>98</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>11017</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>11016</v>
+        <v>11021</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>11014</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>11020</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>11018</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>11015</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>11013</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>99</v>
+        <v>980001</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>11021</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="71">
@@ -1267,10 +1267,10 @@
         <v>980001</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D71" t="n">
-        <v>980101</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="72">
@@ -1278,10 +1278,10 @@
         <v>980001</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>980102</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="73">
@@ -1289,10 +1289,10 @@
         <v>980001</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>980103</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="74">
@@ -1300,10 +1300,10 @@
         <v>980001</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
-        <v>980104</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="75">
@@ -1311,10 +1311,10 @@
         <v>980001</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
-        <v>980105</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="76">
@@ -1322,10 +1322,10 @@
         <v>980001</v>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>980106</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="77">
@@ -1333,10 +1333,10 @@
         <v>980001</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D77" t="n">
-        <v>980107</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="78">
@@ -1344,76 +1344,76 @@
         <v>980001</v>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>980108</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>980109</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>980110</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>980111</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>980112</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C83" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>980113</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C84" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>980114</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="85">
@@ -1421,10 +1421,10 @@
         <v>990001</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>990101</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="86">
@@ -1432,76 +1432,76 @@
         <v>990001</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
-        <v>990102</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>990103</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>990104</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>990105</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>990106</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>990107</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D92" t="n">
-        <v>990108</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="93">
@@ -1509,120 +1509,120 @@
         <v>1000001</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>1000101</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1000102</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>1000103</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>1000104</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>1000105</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1000106</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1000109</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>1010101</v>
+        <v>1020103</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>1010102</v>
+        <v>1020104</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
-        <v>1010103</v>
+        <v>1020105</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
-        <v>1010104</v>
+        <v>1020106</v>
       </c>
     </row>
     <row r="104">
@@ -1630,10 +1630,10 @@
         <v>1020001</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>1020101</v>
+        <v>1020107</v>
       </c>
     </row>
     <row r="105">
@@ -1641,10 +1641,10 @@
         <v>1020001</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
-        <v>1020102</v>
+        <v>1020108</v>
       </c>
     </row>
     <row r="106">
@@ -1652,76 +1652,76 @@
         <v>1020001</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>1020103</v>
+        <v>1020109</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1020104</v>
+        <v>1030101</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1020105</v>
+        <v>1030102</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>1020106</v>
+        <v>1030103</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>1020107</v>
+        <v>1030104</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>1020108</v>
+        <v>1030105</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>1020109</v>
+        <v>1030106</v>
       </c>
     </row>
     <row r="113">
@@ -1729,10 +1729,10 @@
         <v>1030001</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>1030101</v>
+        <v>1030108</v>
       </c>
     </row>
     <row r="114">
@@ -1740,76 +1740,76 @@
         <v>1030001</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D114" t="n">
-        <v>1030102</v>
+        <v>1030109</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>1030103</v>
+        <v>1040101</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>1030104</v>
+        <v>1040102</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>1030105</v>
+        <v>1040103</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
-        <v>1030106</v>
+        <v>1040104</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C119" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D119" t="n">
-        <v>1030108</v>
+        <v>1040105</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D120" t="n">
-        <v>1030109</v>
+        <v>1040106</v>
       </c>
     </row>
     <row r="121">
@@ -1817,10 +1817,10 @@
         <v>1040001</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>1040101</v>
+        <v>1040107</v>
       </c>
     </row>
     <row r="122">
@@ -1828,10 +1828,10 @@
         <v>1040001</v>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
-        <v>1040102</v>
+        <v>1040108</v>
       </c>
     </row>
     <row r="123">
@@ -1839,10 +1839,10 @@
         <v>1040001</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>1040103</v>
+        <v>1040112</v>
       </c>
     </row>
     <row r="124">
@@ -1850,120 +1850,120 @@
         <v>1040001</v>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>1040104</v>
+        <v>1040113</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>1040105</v>
+        <v>1050101</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>1040106</v>
+        <v>1050102</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>1040107</v>
+        <v>1050103</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C128" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
-        <v>1040108</v>
+        <v>1050104</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>1040112</v>
+        <v>1060101</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>1040113</v>
+        <v>1060102</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>1050101</v>
+        <v>1060103</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>1050102</v>
+        <v>1060104</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D133" t="n">
-        <v>1050103</v>
+        <v>1060105</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D134" t="n">
-        <v>1050104</v>
+        <v>1060106</v>
       </c>
     </row>
     <row r="135">
@@ -1971,10 +1971,10 @@
         <v>1060001</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>1060101</v>
+        <v>1060107</v>
       </c>
     </row>
     <row r="136">
@@ -1982,10 +1982,10 @@
         <v>1060001</v>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D136" t="n">
-        <v>1060102</v>
+        <v>1060108</v>
       </c>
     </row>
     <row r="137">
@@ -1993,76 +1993,76 @@
         <v>1060001</v>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D137" t="n">
-        <v>1060103</v>
+        <v>1060109</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>1060104</v>
+        <v>1070101</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>1060105</v>
+        <v>1070102</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>1060106</v>
+        <v>1070103</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C141" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
-        <v>1060107</v>
+        <v>1070104</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C142" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D142" t="n">
-        <v>1060108</v>
+        <v>1070105</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>1060109</v>
+        <v>1070106</v>
       </c>
     </row>
     <row r="144">
@@ -2070,10 +2070,10 @@
         <v>1070001</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D144" t="n">
-        <v>1070101</v>
+        <v>1070107</v>
       </c>
     </row>
     <row r="145">
@@ -2081,10 +2081,10 @@
         <v>1070001</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D145" t="n">
-        <v>1070102</v>
+        <v>1070108</v>
       </c>
     </row>
     <row r="146">
@@ -2092,10 +2092,10 @@
         <v>1070001</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D146" t="n">
-        <v>1070103</v>
+        <v>1070109</v>
       </c>
     </row>
     <row r="147">
@@ -2103,76 +2103,76 @@
         <v>1070001</v>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D147" t="n">
-        <v>1070104</v>
+        <v>1070110</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1070105</v>
+        <v>1080101</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>1070106</v>
+        <v>1080102</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>1070107</v>
+        <v>1080103</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C151" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D151" t="n">
-        <v>1070108</v>
+        <v>1080104</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C152" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D152" t="n">
-        <v>1070109</v>
+        <v>1080105</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C153" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D153" t="n">
-        <v>1070110</v>
+        <v>1080106</v>
       </c>
     </row>
     <row r="154">
@@ -2180,76 +2180,384 @@
         <v>1080001</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D154" t="n">
-        <v>1080101</v>
+        <v>1080107</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1080102</v>
+        <v>1090102</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>1080103</v>
+        <v>1090103</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1080104</v>
+        <v>1090122</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>1080105</v>
+        <v>1090123</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>1080106</v>
+        <v>1090124</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>1080107</v>
+        <v>1090142</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1090143</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1090144</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1090162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1090163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1090182</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1090202</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1090203</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1090204</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>96</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1090222</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>96</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1090223</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>96</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1090224</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>96</v>
+      </c>
+      <c r="C172" t="n">
+        <v>4</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1090225</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1090242</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C174" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1090243</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1090244</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C176" t="n">
+        <v>4</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1090245</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1090262</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1090282</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1090283</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1090284</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C181" t="n">
+        <v>4</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1090285</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1090302</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1090303</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1090304</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1090305</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1090306</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1090322</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1090323</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,123 +571,123 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>11025</v>
+        <v>11027</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>11023</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>11024</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>11022</v>
+        <v>11029</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11026</v>
+        <v>11031</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11027</v>
+        <v>11032</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11028</v>
+        <v>11038</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>11030</v>
+        <v>11033</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11029</v>
+        <v>11039</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>11031</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>11032</v>
+        <v>11046</v>
       </c>
     </row>
     <row r="19">
@@ -695,10 +695,10 @@
         <v>105</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>11038</v>
+        <v>11037</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         <v>105</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>11033</v>
+        <v>11041</v>
       </c>
     </row>
     <row r="21">
@@ -717,10 +717,10 @@
         <v>105</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>11039</v>
+        <v>11043</v>
       </c>
     </row>
     <row r="22">
@@ -728,10 +728,10 @@
         <v>105</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>11040</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="23">
@@ -739,10 +739,10 @@
         <v>105</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>11046</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="24">
@@ -750,10 +750,10 @@
         <v>105</v>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>11037</v>
+        <v>11044</v>
       </c>
     </row>
     <row r="25">
@@ -761,10 +761,10 @@
         <v>105</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>11041</v>
+        <v>11045</v>
       </c>
     </row>
     <row r="26">
@@ -772,10 +772,10 @@
         <v>105</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>11043</v>
+        <v>11042</v>
       </c>
     </row>
     <row r="27">
@@ -783,417 +783,417 @@
         <v>105</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>11034</v>
+        <v>11036</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>11035</v>
+        <v>11047</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>11044</v>
+        <v>11048</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>11045</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>11042</v>
+        <v>11049</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>11036</v>
+        <v>11052</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>11047</v>
+        <v>11053</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>11048</v>
+        <v>11051</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>11050</v>
+        <v>11055</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>11049</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>11052</v>
+        <v>11057</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>11053</v>
+        <v>11058</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>11051</v>
+        <v>11056</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>11055</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>11054</v>
+        <v>11060</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>11057</v>
+        <v>11063</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>11058</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>11056</v>
+        <v>11059</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>11062</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>11060</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>11063</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C48" t="n">
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>11061</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C49" t="n">
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>11059</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>11008</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>11011</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>11009</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>11007</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>11010</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>11012</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>11019</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>11017</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>11016</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>11014</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>11020</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>11018</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>11015</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>11013</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>99</v>
+        <v>980001</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
-        <v>11021</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="65">
@@ -1201,10 +1201,10 @@
         <v>980001</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D65" t="n">
-        <v>980101</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="66">
@@ -1212,10 +1212,10 @@
         <v>980001</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D66" t="n">
-        <v>980102</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="67">
@@ -1223,1341 +1223,1627 @@
         <v>980001</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D67" t="n">
-        <v>980103</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>980104</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>980105</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>980106</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>980107</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>980108</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>980109</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>980110</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C75" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D75" t="n">
-        <v>980111</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C76" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>980112</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C77" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>980113</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C78" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>980114</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>990101</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>990102</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>990103</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>990104</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>990105</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>990106</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>990107</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>990108</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1000101</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1000102</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C89" t="n">
         <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1000103</v>
+        <v>1020103</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C90" t="n">
         <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>1000104</v>
+        <v>1020104</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C91" t="n">
         <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>1000105</v>
+        <v>1020105</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C92" t="n">
         <v>6</v>
       </c>
       <c r="D92" t="n">
-        <v>1000106</v>
+        <v>1020106</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C93" t="n">
         <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>1000109</v>
+        <v>1020107</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
-        <v>1010101</v>
+        <v>1020108</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D95" t="n">
-        <v>1010102</v>
+        <v>1020109</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1010103</v>
+        <v>1030101</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1010104</v>
+        <v>1030102</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>1020101</v>
+        <v>1030103</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>1020102</v>
+        <v>1030104</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D100" t="n">
-        <v>1020103</v>
+        <v>1030105</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>1020104</v>
+        <v>1030106</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D102" t="n">
-        <v>1020105</v>
+        <v>1030108</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D103" t="n">
-        <v>1020106</v>
+        <v>1030109</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1020107</v>
+        <v>1040101</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>1020108</v>
+        <v>1040102</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1020109</v>
+        <v>1040103</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>1030101</v>
+        <v>1040104</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>1030102</v>
+        <v>1040105</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D109" t="n">
-        <v>1030103</v>
+        <v>1040106</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
-        <v>1030104</v>
+        <v>1040107</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D111" t="n">
-        <v>1030105</v>
+        <v>1040108</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>1030106</v>
+        <v>1040112</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>1030108</v>
+        <v>1040113</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>1030109</v>
+        <v>1050101</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>1040101</v>
+        <v>1050102</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>1040102</v>
+        <v>1050103</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>1040103</v>
+        <v>1050104</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>1040104</v>
+        <v>1060101</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>1040105</v>
+        <v>1060102</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>1040106</v>
+        <v>1060103</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>1040107</v>
+        <v>1060104</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D122" t="n">
-        <v>1040108</v>
+        <v>1060105</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>1040112</v>
+        <v>1060106</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
-        <v>1040113</v>
+        <v>1060107</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>1050101</v>
+        <v>1060108</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D126" t="n">
-        <v>1050102</v>
+        <v>1060109</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>1050103</v>
+        <v>1070101</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>1050104</v>
+        <v>1070102</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>1060101</v>
+        <v>1070103</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>1060102</v>
+        <v>1070104</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>1060103</v>
+        <v>1070105</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D132" t="n">
-        <v>1060104</v>
+        <v>1070106</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
-        <v>1060105</v>
+        <v>1070107</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D134" t="n">
-        <v>1060106</v>
+        <v>1070108</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D135" t="n">
-        <v>1060107</v>
+        <v>1070109</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D136" t="n">
-        <v>1060108</v>
+        <v>1070110</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>1060109</v>
+        <v>1080101</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>1070101</v>
+        <v>1080102</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>1070102</v>
+        <v>1080103</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>1070103</v>
+        <v>1080104</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D141" t="n">
-        <v>1070104</v>
+        <v>1080105</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D142" t="n">
-        <v>1070105</v>
+        <v>1080106</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D143" t="n">
-        <v>1070106</v>
+        <v>1080107</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C144" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1070107</v>
+        <v>1090102</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C145" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1070108</v>
+        <v>1090103</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1070001</v>
+        <v>1090002</v>
       </c>
       <c r="C146" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>1070109</v>
+        <v>1090122</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1070001</v>
+        <v>1090002</v>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>1070110</v>
+        <v>1090123</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>1080101</v>
+        <v>1090124</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>1080102</v>
+        <v>1090142</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>1080103</v>
+        <v>1090143</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>1080104</v>
+        <v>1090144</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1080001</v>
+        <v>1090004</v>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1080105</v>
+        <v>1090162</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1080001</v>
+        <v>1090004</v>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>1080106</v>
+        <v>1090163</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1080001</v>
+        <v>1090005</v>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1080107</v>
+        <v>1090182</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>95</v>
+        <v>1090006</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1090102</v>
+        <v>1090202</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>95</v>
+        <v>1090006</v>
       </c>
       <c r="C156" t="n">
         <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>1090103</v>
+        <v>1090203</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1090002</v>
+        <v>1090006</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>1090122</v>
+        <v>1090204</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1090002</v>
+        <v>96</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>1090123</v>
+        <v>1090222</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1090002</v>
+        <v>96</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>1090124</v>
+        <v>1090223</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1090003</v>
+        <v>96</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>1090142</v>
+        <v>1090224</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1090003</v>
+        <v>96</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>1090143</v>
+        <v>1090225</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1090003</v>
+        <v>1090008</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1090144</v>
+        <v>1090242</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1090004</v>
+        <v>1090008</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>1090162</v>
+        <v>1090243</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1090004</v>
+        <v>1090008</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>1090163</v>
+        <v>1090244</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>1090182</v>
+        <v>1090245</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>1090202</v>
+        <v>1090262</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1090006</v>
+        <v>1090010</v>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1090203</v>
+        <v>1090282</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1090006</v>
+        <v>1090010</v>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>1090204</v>
+        <v>1090283</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>1090222</v>
+        <v>1090284</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>1090223</v>
+        <v>1090285</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1090224</v>
+        <v>1090302</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>1090225</v>
+        <v>1090303</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1090242</v>
+        <v>1090304</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>1090243</v>
+        <v>1090305</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D175" t="n">
-        <v>1090244</v>
+        <v>1090306</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1090008</v>
+        <v>1090012</v>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1090245</v>
+        <v>1090322</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>1090262</v>
+        <v>1090323</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1090282</v>
+        <v>1100102</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C179" t="n">
         <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>1090283</v>
+        <v>1100103</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C180" t="n">
         <v>3</v>
       </c>
       <c r="D180" t="n">
-        <v>1090284</v>
+        <v>1100104</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C181" t="n">
         <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>1090285</v>
+        <v>1100105</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1090011</v>
+        <v>1100002</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1090302</v>
+        <v>1100122</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1090011</v>
+        <v>1100003</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>1090303</v>
+        <v>1100142</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1090011</v>
+        <v>1100003</v>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>1090304</v>
+        <v>1100143</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1090011</v>
+        <v>1100004</v>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>1090305</v>
+        <v>1100162</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1090011</v>
+        <v>1100004</v>
       </c>
       <c r="C186" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>1090306</v>
+        <v>1100163</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1090012</v>
+        <v>1100004</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>1090322</v>
+        <v>1100164</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1090012</v>
+        <v>1100004</v>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D188" t="n">
-        <v>1090323</v>
+        <v>1100165</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>99</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1100182</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1100202</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1100203</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1100204</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1100222</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1100223</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1100224</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1100225</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>100</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1100242</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>100</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1100243</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>100</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1100244</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>100</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1100245</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1100262</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1100263</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1100264</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C204" t="n">
+        <v>4</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1100265</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C205" t="n">
+        <v>5</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1100266</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1100282</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1100283</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1100284</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1100285</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C210" t="n">
+        <v>5</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1100286</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1100302</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1100322</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C213" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1100323</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1100324</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J214"/>
+  <dimension ref="A1:J238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,46 +593,46 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>11030</v>
+        <v>11038</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>11029</v>
+        <v>11033</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11031</v>
+        <v>11039</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11032</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="14">
@@ -640,10 +640,10 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>11038</v>
+        <v>11046</v>
       </c>
     </row>
     <row r="15">
@@ -651,10 +651,10 @@
         <v>105</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>11033</v>
+        <v>11037</v>
       </c>
     </row>
     <row r="16">
@@ -662,10 +662,10 @@
         <v>105</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>11039</v>
+        <v>11041</v>
       </c>
     </row>
     <row r="17">
@@ -673,10 +673,10 @@
         <v>105</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>11040</v>
+        <v>11043</v>
       </c>
     </row>
     <row r="18">
@@ -684,10 +684,10 @@
         <v>105</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>11046</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="19">
@@ -695,10 +695,10 @@
         <v>105</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>11037</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         <v>105</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>11041</v>
+        <v>11044</v>
       </c>
     </row>
     <row r="21">
@@ -717,10 +717,10 @@
         <v>105</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>11043</v>
+        <v>11045</v>
       </c>
     </row>
     <row r="22">
@@ -728,10 +728,10 @@
         <v>105</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>11034</v>
+        <v>11042</v>
       </c>
     </row>
     <row r="23">
@@ -739,186 +739,186 @@
         <v>105</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>11035</v>
+        <v>11036</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11044</v>
+        <v>11047</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11045</v>
+        <v>11048</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>11042</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>11036</v>
+        <v>11049</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>11047</v>
+        <v>11052</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>11048</v>
+        <v>11053</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>11050</v>
+        <v>11051</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>11049</v>
+        <v>11055</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>11052</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>11053</v>
+        <v>11057</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>11051</v>
+        <v>11058</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>11055</v>
+        <v>11056</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>11054</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>11057</v>
+        <v>11060</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>11058</v>
+        <v>11063</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>11056</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="40">
@@ -926,54 +926,54 @@
         <v>111</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>11062</v>
+        <v>11059</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>11060</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>11063</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>11061</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>11059</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="45">
@@ -981,10 +981,10 @@
         <v>98</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>11012</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="46">
@@ -992,10 +992,10 @@
         <v>98</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>11019</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="47">
@@ -1003,10 +1003,10 @@
         <v>98</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>11017</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="48">
@@ -1014,10 +1014,10 @@
         <v>98</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>11016</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="49">
@@ -1025,54 +1025,54 @@
         <v>98</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>11014</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>11020</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>11018</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>11015</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>11013</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="54">
@@ -1080,10 +1080,10 @@
         <v>980001</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>980101</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="55">
@@ -1091,10 +1091,10 @@
         <v>980001</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>980102</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="56">
@@ -1102,10 +1102,10 @@
         <v>980001</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>980103</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="57">
@@ -1113,10 +1113,10 @@
         <v>980001</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>980104</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="58">
@@ -1124,10 +1124,10 @@
         <v>980001</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>980105</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="59">
@@ -1135,10 +1135,10 @@
         <v>980001</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>980106</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="60">
@@ -1146,10 +1146,10 @@
         <v>980001</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>980107</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="61">
@@ -1157,10 +1157,10 @@
         <v>980001</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>980108</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="62">
@@ -1168,10 +1168,10 @@
         <v>980001</v>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>980109</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="63">
@@ -1179,54 +1179,54 @@
         <v>980001</v>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>980110</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>980111</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C65" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>980112</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>980113</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C67" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>980114</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="68">
@@ -1234,10 +1234,10 @@
         <v>990001</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>990101</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="69">
@@ -1245,10 +1245,10 @@
         <v>990001</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>990102</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="70">
@@ -1256,10 +1256,10 @@
         <v>990001</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>990103</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="71">
@@ -1267,54 +1267,54 @@
         <v>990001</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>990104</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>990105</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>990106</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>990107</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>990108</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="76">
@@ -1322,10 +1322,10 @@
         <v>1000001</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>1000101</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="77">
@@ -1333,10 +1333,10 @@
         <v>1000001</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>1000102</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="78">
@@ -1344,98 +1344,98 @@
         <v>1000001</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>1000103</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1000104</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1000105</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1000106</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>1000109</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1010101</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>1010102</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>1010103</v>
+        <v>1020103</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C86" t="n">
         <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>1010104</v>
+        <v>1020104</v>
       </c>
     </row>
     <row r="87">
@@ -1443,10 +1443,10 @@
         <v>1020001</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>1020101</v>
+        <v>1020105</v>
       </c>
     </row>
     <row r="88">
@@ -1454,10 +1454,10 @@
         <v>1020001</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D88" t="n">
-        <v>1020102</v>
+        <v>1020106</v>
       </c>
     </row>
     <row r="89">
@@ -1465,10 +1465,10 @@
         <v>1020001</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>1020103</v>
+        <v>1020107</v>
       </c>
     </row>
     <row r="90">
@@ -1476,10 +1476,10 @@
         <v>1020001</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D90" t="n">
-        <v>1020104</v>
+        <v>1020108</v>
       </c>
     </row>
     <row r="91">
@@ -1487,54 +1487,54 @@
         <v>1020001</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D91" t="n">
-        <v>1020105</v>
+        <v>1020109</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1020106</v>
+        <v>1030101</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>1020107</v>
+        <v>1030102</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1020108</v>
+        <v>1030103</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>1020109</v>
+        <v>1030104</v>
       </c>
     </row>
     <row r="96">
@@ -1542,10 +1542,10 @@
         <v>1030001</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>1030101</v>
+        <v>1030105</v>
       </c>
     </row>
     <row r="97">
@@ -1553,10 +1553,10 @@
         <v>1030001</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>1030102</v>
+        <v>1030106</v>
       </c>
     </row>
     <row r="98">
@@ -1564,10 +1564,10 @@
         <v>1030001</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>1030103</v>
+        <v>1030108</v>
       </c>
     </row>
     <row r="99">
@@ -1575,54 +1575,54 @@
         <v>1030001</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D99" t="n">
-        <v>1030104</v>
+        <v>1030109</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1030105</v>
+        <v>1040101</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>1030106</v>
+        <v>1040102</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>1030108</v>
+        <v>1040103</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>1030109</v>
+        <v>1040104</v>
       </c>
     </row>
     <row r="104">
@@ -1630,10 +1630,10 @@
         <v>1040001</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>1040101</v>
+        <v>1040105</v>
       </c>
     </row>
     <row r="105">
@@ -1641,10 +1641,10 @@
         <v>1040001</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>1040102</v>
+        <v>1040106</v>
       </c>
     </row>
     <row r="106">
@@ -1652,10 +1652,10 @@
         <v>1040001</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D106" t="n">
-        <v>1040103</v>
+        <v>1040107</v>
       </c>
     </row>
     <row r="107">
@@ -1663,10 +1663,10 @@
         <v>1040001</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>1040104</v>
+        <v>1040108</v>
       </c>
     </row>
     <row r="108">
@@ -1674,10 +1674,10 @@
         <v>1040001</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D108" t="n">
-        <v>1040105</v>
+        <v>1040112</v>
       </c>
     </row>
     <row r="109">
@@ -1685,98 +1685,98 @@
         <v>1040001</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D109" t="n">
-        <v>1040106</v>
+        <v>1040113</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>1040107</v>
+        <v>1050101</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>1040108</v>
+        <v>1050102</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>1040112</v>
+        <v>1050103</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
-        <v>1040113</v>
+        <v>1050104</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>1050101</v>
+        <v>1060101</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C115" t="n">
         <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>1050102</v>
+        <v>1060102</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C116" t="n">
         <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>1050103</v>
+        <v>1060103</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C117" t="n">
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>1050104</v>
+        <v>1060104</v>
       </c>
     </row>
     <row r="118">
@@ -1784,10 +1784,10 @@
         <v>1060001</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D118" t="n">
-        <v>1060101</v>
+        <v>1060105</v>
       </c>
     </row>
     <row r="119">
@@ -1795,10 +1795,10 @@
         <v>1060001</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>1060102</v>
+        <v>1060106</v>
       </c>
     </row>
     <row r="120">
@@ -1806,10 +1806,10 @@
         <v>1060001</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D120" t="n">
-        <v>1060103</v>
+        <v>1060107</v>
       </c>
     </row>
     <row r="121">
@@ -1817,10 +1817,10 @@
         <v>1060001</v>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D121" t="n">
-        <v>1060104</v>
+        <v>1060108</v>
       </c>
     </row>
     <row r="122">
@@ -1828,54 +1828,54 @@
         <v>1060001</v>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D122" t="n">
-        <v>1060105</v>
+        <v>1060109</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>1060106</v>
+        <v>1070101</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>1060107</v>
+        <v>1070102</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>1060108</v>
+        <v>1070103</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>1060109</v>
+        <v>1070104</v>
       </c>
     </row>
     <row r="127">
@@ -1883,10 +1883,10 @@
         <v>1070001</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D127" t="n">
-        <v>1070101</v>
+        <v>1070105</v>
       </c>
     </row>
     <row r="128">
@@ -1894,10 +1894,10 @@
         <v>1070001</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>1070102</v>
+        <v>1070106</v>
       </c>
     </row>
     <row r="129">
@@ -1905,10 +1905,10 @@
         <v>1070001</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>1070103</v>
+        <v>1070107</v>
       </c>
     </row>
     <row r="130">
@@ -1916,10 +1916,10 @@
         <v>1070001</v>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D130" t="n">
-        <v>1070104</v>
+        <v>1070108</v>
       </c>
     </row>
     <row r="131">
@@ -1927,10 +1927,10 @@
         <v>1070001</v>
       </c>
       <c r="C131" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D131" t="n">
-        <v>1070105</v>
+        <v>1070109</v>
       </c>
     </row>
     <row r="132">
@@ -1938,54 +1938,54 @@
         <v>1070001</v>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>1070106</v>
+        <v>1070110</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>1070107</v>
+        <v>1080101</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C134" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>1070108</v>
+        <v>1080102</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>1070109</v>
+        <v>1080103</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C136" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D136" t="n">
-        <v>1070110</v>
+        <v>1080104</v>
       </c>
     </row>
     <row r="137">
@@ -1993,10 +1993,10 @@
         <v>1080001</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D137" t="n">
-        <v>1080101</v>
+        <v>1080105</v>
       </c>
     </row>
     <row r="138">
@@ -2004,10 +2004,10 @@
         <v>1080001</v>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D138" t="n">
-        <v>1080102</v>
+        <v>1080106</v>
       </c>
     </row>
     <row r="139">
@@ -2015,351 +2015,351 @@
         <v>1080001</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>1080103</v>
+        <v>1080107</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>1080104</v>
+        <v>1090102</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>1080105</v>
+        <v>1090103</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1080106</v>
+        <v>1090122</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>1080107</v>
+        <v>1090123</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>1090102</v>
+        <v>1090124</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1090103</v>
+        <v>1090142</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>1090122</v>
+        <v>1090143</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>1090123</v>
+        <v>1090144</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1090124</v>
+        <v>1090162</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>1090142</v>
+        <v>1090163</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1090003</v>
+        <v>1090005</v>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>1090143</v>
+        <v>1090182</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1090144</v>
+        <v>1090202</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>1090162</v>
+        <v>1090203</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>1090163</v>
+        <v>1090204</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1090182</v>
+        <v>1090222</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>1090202</v>
+        <v>1090223</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>1090203</v>
+        <v>1090224</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
-        <v>1090204</v>
+        <v>1090225</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>1090222</v>
+        <v>1090242</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C159" t="n">
         <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>1090223</v>
+        <v>1090243</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C160" t="n">
         <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>1090224</v>
+        <v>1090244</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C161" t="n">
         <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>1090225</v>
+        <v>1090245</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1090008</v>
+        <v>1090009</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1090242</v>
+        <v>1090262</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>1090243</v>
+        <v>1090282</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>1090244</v>
+        <v>1090283</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>1090245</v>
+        <v>1090284</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>1090262</v>
+        <v>1090285</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1090282</v>
+        <v>1090302</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C168" t="n">
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>1090283</v>
+        <v>1090303</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C169" t="n">
         <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>1090284</v>
+        <v>1090304</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C170" t="n">
         <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>1090285</v>
+        <v>1090305</v>
       </c>
     </row>
     <row r="171">
@@ -2367,329 +2367,329 @@
         <v>1090011</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D171" t="n">
-        <v>1090302</v>
+        <v>1090306</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1090303</v>
+        <v>1090322</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>1090304</v>
+        <v>1090323</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C174" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1090305</v>
+        <v>1100102</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>1090306</v>
+        <v>1100103</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>1090322</v>
+        <v>1100104</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>1090323</v>
+        <v>1100105</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>97</v>
+        <v>1100002</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1100102</v>
+        <v>1100122</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1100103</v>
+        <v>1100142</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>1100104</v>
+        <v>1100143</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>1100105</v>
+        <v>1100162</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1100002</v>
+        <v>1100004</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="n">
-        <v>1100122</v>
+        <v>1100163</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>1100142</v>
+        <v>1100164</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D184" t="n">
-        <v>1100143</v>
+        <v>1100165</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1100004</v>
+        <v>99</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>1100162</v>
+        <v>1100182</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>1100163</v>
+        <v>1100202</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D187" t="n">
-        <v>1100164</v>
+        <v>1100203</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>1100165</v>
+        <v>1100204</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>99</v>
+        <v>1100007</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>1100182</v>
+        <v>1100222</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
-        <v>1100202</v>
+        <v>1100223</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>1100203</v>
+        <v>1100224</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D192" t="n">
-        <v>1100204</v>
+        <v>1100225</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>1100222</v>
+        <v>1100242</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C194" t="n">
         <v>2</v>
       </c>
       <c r="D194" t="n">
-        <v>1100223</v>
+        <v>1100243</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C195" t="n">
         <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>1100224</v>
+        <v>1100244</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C196" t="n">
         <v>4</v>
       </c>
       <c r="D196" t="n">
-        <v>1100225</v>
+        <v>1100245</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>1100242</v>
+        <v>1100262</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C198" t="n">
         <v>2</v>
       </c>
       <c r="D198" t="n">
-        <v>1100243</v>
+        <v>1100263</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C199" t="n">
         <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>1100244</v>
+        <v>1100264</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C200" t="n">
         <v>4</v>
       </c>
       <c r="D200" t="n">
-        <v>1100245</v>
+        <v>1100265</v>
       </c>
     </row>
     <row r="201">
@@ -2697,54 +2697,54 @@
         <v>1100009</v>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D201" t="n">
-        <v>1100262</v>
+        <v>1100266</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>1100263</v>
+        <v>1100282</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D203" t="n">
-        <v>1100264</v>
+        <v>1100283</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C204" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D204" t="n">
-        <v>1100265</v>
+        <v>1100284</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D205" t="n">
-        <v>1100266</v>
+        <v>1100285</v>
       </c>
     </row>
     <row r="206">
@@ -2752,98 +2752,362 @@
         <v>1100010</v>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D206" t="n">
-        <v>1100282</v>
+        <v>1100286</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1100010</v>
+        <v>1100011</v>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>1100283</v>
+        <v>1100302</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>1100284</v>
+        <v>1100322</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D209" t="n">
-        <v>1100285</v>
+        <v>1100323</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C210" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>1100286</v>
+        <v>1100324</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1100011</v>
+        <v>1110001</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>1100302</v>
+        <v>1110102</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D212" t="n">
-        <v>1100322</v>
+        <v>1110103</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D213" t="n">
-        <v>1100323</v>
+        <v>1110104</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D214" t="n">
-        <v>1100324</v>
+        <v>1110105</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1110122</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1110142</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C217" t="n">
+        <v>2</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1110143</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1110144</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1110145</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1110162</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C221" t="n">
+        <v>2</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1110163</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1110164</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1110165</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1110182</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C225" t="n">
+        <v>2</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1110183</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1110184</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1110202</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>102</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1110222</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>102</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1110223</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1110242</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1110262</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>103</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1110282</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1110302</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C234" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1110303</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1110304</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C236" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1110305</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C237" t="n">
+        <v>5</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1110306</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>104</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1110322</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J238"/>
+  <dimension ref="A1:J266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,189 +747,189 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11047</v>
+        <v>11055</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>11048</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11050</v>
+        <v>11057</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>11049</v>
+        <v>11058</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>11052</v>
+        <v>11056</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>11053</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>11051</v>
+        <v>11060</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>11055</v>
+        <v>11063</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>11054</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>11057</v>
+        <v>11059</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>11058</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>11056</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>11062</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>11060</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>11063</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>11061</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>11059</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="41">
@@ -937,10 +937,10 @@
         <v>98</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>11012</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="42">
@@ -948,87 +948,87 @@
         <v>98</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>11019</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>11017</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>11016</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>11014</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>11020</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>11018</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>11015</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>11013</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="50">
@@ -1036,10 +1036,10 @@
         <v>980001</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>980101</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="51">
@@ -1047,10 +1047,10 @@
         <v>980001</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>980102</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="52">
@@ -1058,10 +1058,10 @@
         <v>980001</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>980103</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="53">
@@ -1069,10 +1069,10 @@
         <v>980001</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>980104</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="54">
@@ -1080,10 +1080,10 @@
         <v>980001</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>980105</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="55">
@@ -1091,10 +1091,10 @@
         <v>980001</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
-        <v>980106</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="56">
@@ -1102,87 +1102,87 @@
         <v>980001</v>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D56" t="n">
-        <v>980107</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>980108</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>980109</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>980110</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>980111</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>980112</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>980113</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>980114</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="64">
@@ -1190,208 +1190,208 @@
         <v>990001</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>990101</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>990102</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>990103</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>990104</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>990105</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>990106</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>990107</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" t="n">
-        <v>990108</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1000101</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>1000102</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>1000103</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C75" t="n">
         <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>1000104</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1000105</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>1000106</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>1000109</v>
+        <v>1020103</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>1010101</v>
+        <v>1020104</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>1010102</v>
+        <v>1020105</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>1010103</v>
+        <v>1020106</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>1010104</v>
+        <v>1020107</v>
       </c>
     </row>
     <row r="83">
@@ -1399,10 +1399,10 @@
         <v>1020001</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>1020101</v>
+        <v>1020108</v>
       </c>
     </row>
     <row r="84">
@@ -1410,87 +1410,87 @@
         <v>1020001</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>1020102</v>
+        <v>1020109</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1020103</v>
+        <v>1030101</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>1020104</v>
+        <v>1030102</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1020105</v>
+        <v>1030103</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>1020106</v>
+        <v>1030104</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>1020107</v>
+        <v>1030105</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>1020108</v>
+        <v>1030106</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>1020109</v>
+        <v>1030108</v>
       </c>
     </row>
     <row r="92">
@@ -1498,87 +1498,87 @@
         <v>1030001</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D92" t="n">
-        <v>1030101</v>
+        <v>1030109</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1030102</v>
+        <v>1040101</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>1030103</v>
+        <v>1040102</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>1030104</v>
+        <v>1040103</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>1030105</v>
+        <v>1040104</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>1030106</v>
+        <v>1040105</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>1030108</v>
+        <v>1040106</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>1030109</v>
+        <v>1040107</v>
       </c>
     </row>
     <row r="100">
@@ -1586,10 +1586,10 @@
         <v>1040001</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>1040101</v>
+        <v>1040108</v>
       </c>
     </row>
     <row r="101">
@@ -1597,10 +1597,10 @@
         <v>1040001</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>1040102</v>
+        <v>1040112</v>
       </c>
     </row>
     <row r="102">
@@ -1608,131 +1608,131 @@
         <v>1040001</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>1040103</v>
+        <v>1040113</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>1040104</v>
+        <v>1050101</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>1040105</v>
+        <v>1050102</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>1040106</v>
+        <v>1050103</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>1040107</v>
+        <v>1050104</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1040108</v>
+        <v>1060101</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1040112</v>
+        <v>1060102</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>1040113</v>
+        <v>1060103</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>1050101</v>
+        <v>1060104</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>1050102</v>
+        <v>1060105</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>1050103</v>
+        <v>1060106</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>1050104</v>
+        <v>1060107</v>
       </c>
     </row>
     <row r="114">
@@ -1740,10 +1740,10 @@
         <v>1060001</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D114" t="n">
-        <v>1060101</v>
+        <v>1060108</v>
       </c>
     </row>
     <row r="115">
@@ -1751,87 +1751,87 @@
         <v>1060001</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D115" t="n">
-        <v>1060102</v>
+        <v>1060109</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>1060103</v>
+        <v>1070101</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>1060104</v>
+        <v>1070102</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>1060105</v>
+        <v>1070103</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>1060106</v>
+        <v>1070104</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D120" t="n">
-        <v>1060107</v>
+        <v>1070105</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
-        <v>1060108</v>
+        <v>1070106</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D122" t="n">
-        <v>1060109</v>
+        <v>1070107</v>
       </c>
     </row>
     <row r="123">
@@ -1839,10 +1839,10 @@
         <v>1070001</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D123" t="n">
-        <v>1070101</v>
+        <v>1070108</v>
       </c>
     </row>
     <row r="124">
@@ -1850,10 +1850,10 @@
         <v>1070001</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
-        <v>1070102</v>
+        <v>1070109</v>
       </c>
     </row>
     <row r="125">
@@ -1861,1253 +1861,1561 @@
         <v>1070001</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D125" t="n">
-        <v>1070103</v>
+        <v>1070110</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>1070104</v>
+        <v>1080101</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>1070105</v>
+        <v>1080102</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>1070106</v>
+        <v>1080103</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C129" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>1070107</v>
+        <v>1080104</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C130" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D130" t="n">
-        <v>1070108</v>
+        <v>1080105</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D131" t="n">
-        <v>1070109</v>
+        <v>1080106</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D132" t="n">
-        <v>1070110</v>
+        <v>1080107</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>1080101</v>
+        <v>1090102</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C134" t="n">
         <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>1080102</v>
+        <v>1090103</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1080103</v>
+        <v>1090122</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>1080104</v>
+        <v>1090123</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>1080105</v>
+        <v>1090124</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>1080106</v>
+        <v>1090142</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C139" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>1080107</v>
+        <v>1090143</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>1090102</v>
+        <v>1090144</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>1090103</v>
+        <v>1090162</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>1090122</v>
+        <v>1090163</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1090002</v>
+        <v>1090005</v>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>1090123</v>
+        <v>1090182</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1090002</v>
+        <v>1090006</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1090124</v>
+        <v>1090202</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1090142</v>
+        <v>1090203</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>1090143</v>
+        <v>1090204</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1090003</v>
+        <v>96</v>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1090144</v>
+        <v>1090222</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>1090162</v>
+        <v>1090223</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>1090163</v>
+        <v>1090224</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D150" t="n">
-        <v>1090182</v>
+        <v>1090225</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1090202</v>
+        <v>1090242</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C152" t="n">
         <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>1090203</v>
+        <v>1090243</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C153" t="n">
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>1090204</v>
+        <v>1090244</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
-        <v>1090222</v>
+        <v>1090245</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>96</v>
+        <v>1090009</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1090223</v>
+        <v>1090262</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1090224</v>
+        <v>1090282</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>1090225</v>
+        <v>1090283</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>1090242</v>
+        <v>1090284</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>1090243</v>
+        <v>1090285</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>1090244</v>
+        <v>1090302</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>1090245</v>
+        <v>1090303</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1090009</v>
+        <v>1090011</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>1090262</v>
+        <v>1090304</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>1090282</v>
+        <v>1090305</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D164" t="n">
-        <v>1090283</v>
+        <v>1090306</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1090010</v>
+        <v>1090012</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1090284</v>
+        <v>1090322</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1090010</v>
+        <v>1090012</v>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D166" t="n">
-        <v>1090285</v>
+        <v>1090323</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1090302</v>
+        <v>1100102</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C168" t="n">
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>1090303</v>
+        <v>1100103</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C169" t="n">
         <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>1090304</v>
+        <v>1100104</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C170" t="n">
         <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>1090305</v>
+        <v>1100105</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1090011</v>
+        <v>1100002</v>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1090306</v>
+        <v>1100122</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1090012</v>
+        <v>1100003</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1090322</v>
+        <v>1100142</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1090012</v>
+        <v>1100003</v>
       </c>
       <c r="C173" t="n">
         <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>1090323</v>
+        <v>1100143</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1100102</v>
+        <v>1100162</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C175" t="n">
         <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>1100103</v>
+        <v>1100163</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C176" t="n">
         <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>1100104</v>
+        <v>1100164</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C177" t="n">
         <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>1100105</v>
+        <v>1100165</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>1100002</v>
+        <v>99</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1100122</v>
+        <v>1100182</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1100003</v>
+        <v>1100006</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1100142</v>
+        <v>1100202</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1100003</v>
+        <v>1100006</v>
       </c>
       <c r="C180" t="n">
         <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>1100143</v>
+        <v>1100203</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>1100162</v>
+        <v>1100204</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1100163</v>
+        <v>1100222</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>1100164</v>
+        <v>1100223</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>1100165</v>
+        <v>1100224</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>99</v>
+        <v>1100007</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>1100182</v>
+        <v>1100225</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1100006</v>
+        <v>100</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>1100202</v>
+        <v>1100242</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1100006</v>
+        <v>100</v>
       </c>
       <c r="C187" t="n">
         <v>2</v>
       </c>
       <c r="D187" t="n">
-        <v>1100203</v>
+        <v>1100243</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1100006</v>
+        <v>100</v>
       </c>
       <c r="C188" t="n">
         <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>1100204</v>
+        <v>1100244</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D189" t="n">
-        <v>1100222</v>
+        <v>1100245</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1100007</v>
+        <v>1100009</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>1100223</v>
+        <v>1100262</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1100007</v>
+        <v>1100009</v>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>1100224</v>
+        <v>1100263</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1100007</v>
+        <v>1100009</v>
       </c>
       <c r="C192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>1100225</v>
+        <v>1100264</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>1100242</v>
+        <v>1100265</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D194" t="n">
-        <v>1100243</v>
+        <v>1100266</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>100</v>
+        <v>1100010</v>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>1100244</v>
+        <v>1100282</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>100</v>
+        <v>1100010</v>
       </c>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
-        <v>1100245</v>
+        <v>1100283</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>1100262</v>
+        <v>1100284</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>1100263</v>
+        <v>1100285</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D199" t="n">
-        <v>1100264</v>
+        <v>1100286</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1100009</v>
+        <v>1100011</v>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>1100265</v>
+        <v>1100302</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1100009</v>
+        <v>1100012</v>
       </c>
       <c r="C201" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>1100266</v>
+        <v>1100322</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D202" t="n">
-        <v>1100282</v>
+        <v>1100323</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>1100283</v>
+        <v>1100324</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>1100284</v>
+        <v>1110102</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C205" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D205" t="n">
-        <v>1100285</v>
+        <v>1110103</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C206" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D206" t="n">
-        <v>1100286</v>
+        <v>1110104</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1100011</v>
+        <v>1110001</v>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D207" t="n">
-        <v>1100302</v>
+        <v>1110105</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1100012</v>
+        <v>1110002</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>1100322</v>
+        <v>1110122</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1100012</v>
+        <v>1110003</v>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>1100323</v>
+        <v>1110142</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1100012</v>
+        <v>1110003</v>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D210" t="n">
-        <v>1100324</v>
+        <v>1110143</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>1110102</v>
+        <v>1110144</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C212" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D212" t="n">
-        <v>1110103</v>
+        <v>1110145</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1110001</v>
+        <v>1110004</v>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>1110104</v>
+        <v>1110162</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1110001</v>
+        <v>1110004</v>
       </c>
       <c r="C214" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D214" t="n">
-        <v>1110105</v>
+        <v>1110163</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1110002</v>
+        <v>1110004</v>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>1110122</v>
+        <v>1110164</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D216" t="n">
-        <v>1110142</v>
+        <v>1110165</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1110003</v>
+        <v>1110005</v>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>1110143</v>
+        <v>1110182</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>1110003</v>
+        <v>1110005</v>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D218" t="n">
-        <v>1110144</v>
+        <v>1110183</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>1110003</v>
+        <v>1110005</v>
       </c>
       <c r="C219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D219" t="n">
-        <v>1110145</v>
+        <v>1110184</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>1110004</v>
+        <v>1110006</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>1110162</v>
+        <v>1110202</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>1110163</v>
+        <v>1110222</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D222" t="n">
-        <v>1110164</v>
+        <v>1110223</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1110004</v>
+        <v>1110008</v>
       </c>
       <c r="C223" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>1110165</v>
+        <v>1110242</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>1110005</v>
+        <v>1110009</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>1110182</v>
+        <v>1110262</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>1110005</v>
+        <v>103</v>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>1110183</v>
+        <v>1110282</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>1110005</v>
+        <v>1110011</v>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>1110184</v>
+        <v>1110302</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>1110006</v>
+        <v>1110011</v>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227" t="n">
-        <v>1110202</v>
+        <v>1110303</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>102</v>
+        <v>1110011</v>
       </c>
       <c r="C228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>1110222</v>
+        <v>1110304</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>102</v>
+        <v>1110011</v>
       </c>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D229" t="n">
-        <v>1110223</v>
+        <v>1110305</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>1110008</v>
+        <v>1110011</v>
       </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D230" t="n">
-        <v>1110242</v>
+        <v>1110306</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>1110009</v>
+        <v>104</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>1110262</v>
+        <v>1110322</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>103</v>
+        <v>1120001</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>1110282</v>
+        <v>1120102</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" t="n">
-        <v>1110011</v>
+        <v>1120001</v>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233" t="n">
-        <v>1110302</v>
+        <v>1120103</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" t="n">
-        <v>1110011</v>
+        <v>1120002</v>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>1110303</v>
+        <v>1120122</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>1110011</v>
+        <v>1120002</v>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D235" t="n">
-        <v>1110304</v>
+        <v>1120123</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" t="n">
-        <v>1110011</v>
+        <v>1120003</v>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>1110305</v>
+        <v>1120142</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" t="n">
-        <v>1110011</v>
+        <v>1120003</v>
       </c>
       <c r="C237" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D237" t="n">
-        <v>1110306</v>
+        <v>1120143</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" t="n">
-        <v>104</v>
+        <v>1120003</v>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D238" t="n">
-        <v>1110322</v>
+        <v>1120144</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1120145</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C240" t="n">
+        <v>5</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1120146</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C241" t="n">
+        <v>6</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1120147</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C242" t="n">
+        <v>7</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1120148</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1120162</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C244" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1120163</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1120164</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C246" t="n">
+        <v>4</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1120165</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>106</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1120182</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1120202</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1120203</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1120204</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C251" t="n">
+        <v>4</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1120205</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1120222</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C253" t="n">
+        <v>2</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1120223</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1120224</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C255" t="n">
+        <v>4</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1120225</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>107</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1120242</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>107</v>
+      </c>
+      <c r="C257" t="n">
+        <v>2</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1120243</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>108</v>
+      </c>
+      <c r="C258" t="n">
+        <v>1</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1120262</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>108</v>
+      </c>
+      <c r="C259" t="n">
+        <v>2</v>
+      </c>
+      <c r="D259" t="n">
+        <v>1120263</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>108</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1120264</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1120282</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C262" t="n">
+        <v>2</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1120283</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3</v>
+      </c>
+      <c r="D263" t="n">
+        <v>1120284</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1120302</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1120322</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1120323</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:J323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3418,6 +3418,633 @@
         <v>1120323</v>
       </c>
     </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1130102</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1130103</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1130104</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C270" t="n">
+        <v>4</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1130105</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C271" t="n">
+        <v>5</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1130106</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1130122</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C273" t="n">
+        <v>2</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1130123</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1130142</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C275" t="n">
+        <v>2</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1130143</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1130144</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C277" t="n">
+        <v>4</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1130145</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C278" t="n">
+        <v>5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1130146</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1130162</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C280" t="n">
+        <v>2</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1130163</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1130164</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C282" t="n">
+        <v>4</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1130165</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C283" t="n">
+        <v>5</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1130166</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C284" t="n">
+        <v>6</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1130167</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C285" t="n">
+        <v>7</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1130168</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C286" t="n">
+        <v>8</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1130169</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1130182</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C288" t="n">
+        <v>2</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1130183</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1130184</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C290" t="n">
+        <v>4</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1130185</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C291" t="n">
+        <v>5</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1130186</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C292" t="n">
+        <v>6</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1130187</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C293" t="n">
+        <v>7</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1130188</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1130202</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C295" t="n">
+        <v>2</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1130203</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1130204</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1130222</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
+      <c r="D298" t="n">
+        <v>1130242</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C299" t="n">
+        <v>2</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1130243</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C300" t="n">
+        <v>3</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1130244</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C301" t="n">
+        <v>4</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1130245</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C302" t="n">
+        <v>5</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1130246</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1130262</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1130282</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C305" t="n">
+        <v>2</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1130283</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1130284</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C307" t="n">
+        <v>4</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1130285</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C308" t="n">
+        <v>5</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1130286</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C309" t="n">
+        <v>6</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1130287</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C310" t="n">
+        <v>7</v>
+      </c>
+      <c r="D310" t="n">
+        <v>1130288</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C311" t="n">
+        <v>8</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1130289</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C312" t="n">
+        <v>9</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1130290</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1130302</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C314" t="n">
+        <v>2</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1130303</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1130304</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C316" t="n">
+        <v>4</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1130305</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C317" t="n">
+        <v>5</v>
+      </c>
+      <c r="D317" t="n">
+        <v>1130306</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C318" t="n">
+        <v>6</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1130307</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1130322</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C320" t="n">
+        <v>2</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1130323</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C321" t="n">
+        <v>3</v>
+      </c>
+      <c r="D321" t="n">
+        <v>1130324</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C322" t="n">
+        <v>4</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1130325</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C323" t="n">
+        <v>5</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1130326</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J323"/>
+  <dimension ref="A1:J358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,35 +769,35 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11057</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>11058</v>
+        <v>11060</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>11056</v>
+        <v>11063</v>
       </c>
     </row>
     <row r="29">
@@ -805,10 +805,10 @@
         <v>111</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>11062</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="30">
@@ -816,43 +816,43 @@
         <v>111</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>11060</v>
+        <v>11059</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>11063</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>11061</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>11059</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="34">
@@ -860,10 +860,10 @@
         <v>98</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>11012</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="35">
@@ -871,10 +871,10 @@
         <v>98</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>11019</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="36">
@@ -882,10 +882,10 @@
         <v>98</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>11017</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="37">
@@ -893,10 +893,10 @@
         <v>98</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>11016</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="38">
@@ -904,10 +904,10 @@
         <v>98</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>11014</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="39">
@@ -915,43 +915,43 @@
         <v>98</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>11020</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>11018</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>11015</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>11013</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="43">
@@ -959,10 +959,10 @@
         <v>980001</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>980101</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="44">
@@ -970,10 +970,10 @@
         <v>980001</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>980102</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="45">
@@ -981,10 +981,10 @@
         <v>980001</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>980103</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="46">
@@ -992,10 +992,10 @@
         <v>980001</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>980104</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="47">
@@ -1003,10 +1003,10 @@
         <v>980001</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>980105</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="48">
@@ -1014,10 +1014,10 @@
         <v>980001</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>980106</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="49">
@@ -1025,10 +1025,10 @@
         <v>980001</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>980107</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="50">
@@ -1036,10 +1036,10 @@
         <v>980001</v>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>980108</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="51">
@@ -1047,10 +1047,10 @@
         <v>980001</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
-        <v>980109</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="52">
@@ -1058,10 +1058,10 @@
         <v>980001</v>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D52" t="n">
-        <v>980110</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="53">
@@ -1069,43 +1069,43 @@
         <v>980001</v>
       </c>
       <c r="C53" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D53" t="n">
-        <v>980111</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>980112</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>980113</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>980114</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="57">
@@ -1113,10 +1113,10 @@
         <v>990001</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>990101</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="58">
@@ -1124,10 +1124,10 @@
         <v>990001</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>990102</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="59">
@@ -1135,10 +1135,10 @@
         <v>990001</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>990103</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="60">
@@ -1146,10 +1146,10 @@
         <v>990001</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>990104</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="61">
@@ -1157,43 +1157,43 @@
         <v>990001</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>990105</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>990106</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>990107</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>990108</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="65">
@@ -1201,10 +1201,10 @@
         <v>1000001</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1000101</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="66">
@@ -1212,10 +1212,10 @@
         <v>1000001</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>1000102</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         <v>1000001</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>1000103</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="68">
@@ -1234,43 +1234,43 @@
         <v>1000001</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>1000104</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1000105</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>1000106</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>1000109</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="72">
@@ -1278,43 +1278,43 @@
         <v>1010001</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>1010101</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>1010102</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>1010103</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>1010104</v>
+        <v>1020103</v>
       </c>
     </row>
     <row r="76">
@@ -1322,10 +1322,10 @@
         <v>1020001</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>1020101</v>
+        <v>1020104</v>
       </c>
     </row>
     <row r="77">
@@ -1333,10 +1333,10 @@
         <v>1020001</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>1020102</v>
+        <v>1020105</v>
       </c>
     </row>
     <row r="78">
@@ -1344,10 +1344,10 @@
         <v>1020001</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>1020103</v>
+        <v>1020106</v>
       </c>
     </row>
     <row r="79">
@@ -1355,10 +1355,10 @@
         <v>1020001</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>1020104</v>
+        <v>1020107</v>
       </c>
     </row>
     <row r="80">
@@ -1366,10 +1366,10 @@
         <v>1020001</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D80" t="n">
-        <v>1020105</v>
+        <v>1020108</v>
       </c>
     </row>
     <row r="81">
@@ -1377,43 +1377,43 @@
         <v>1020001</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>1020106</v>
+        <v>1020109</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1020107</v>
+        <v>1030101</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>1020108</v>
+        <v>1030102</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>1020109</v>
+        <v>1030103</v>
       </c>
     </row>
     <row r="85">
@@ -1421,10 +1421,10 @@
         <v>1030001</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>1030101</v>
+        <v>1030104</v>
       </c>
     </row>
     <row r="86">
@@ -1432,10 +1432,10 @@
         <v>1030001</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>1030102</v>
+        <v>1030105</v>
       </c>
     </row>
     <row r="87">
@@ -1443,10 +1443,10 @@
         <v>1030001</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>1030103</v>
+        <v>1030106</v>
       </c>
     </row>
     <row r="88">
@@ -1454,10 +1454,10 @@
         <v>1030001</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>1030104</v>
+        <v>1030108</v>
       </c>
     </row>
     <row r="89">
@@ -1465,43 +1465,43 @@
         <v>1030001</v>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
-        <v>1030105</v>
+        <v>1030109</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1030106</v>
+        <v>1040101</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>1030108</v>
+        <v>1040102</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1030109</v>
+        <v>1040103</v>
       </c>
     </row>
     <row r="93">
@@ -1509,10 +1509,10 @@
         <v>1040001</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>1040101</v>
+        <v>1040104</v>
       </c>
     </row>
     <row r="94">
@@ -1520,10 +1520,10 @@
         <v>1040001</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>1040102</v>
+        <v>1040105</v>
       </c>
     </row>
     <row r="95">
@@ -1531,10 +1531,10 @@
         <v>1040001</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>1040103</v>
+        <v>1040106</v>
       </c>
     </row>
     <row r="96">
@@ -1542,10 +1542,10 @@
         <v>1040001</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D96" t="n">
-        <v>1040104</v>
+        <v>1040107</v>
       </c>
     </row>
     <row r="97">
@@ -1553,10 +1553,10 @@
         <v>1040001</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>1040105</v>
+        <v>1040108</v>
       </c>
     </row>
     <row r="98">
@@ -1564,10 +1564,10 @@
         <v>1040001</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>1040106</v>
+        <v>1040112</v>
       </c>
     </row>
     <row r="99">
@@ -1575,43 +1575,43 @@
         <v>1040001</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>1040107</v>
+        <v>1040113</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1040108</v>
+        <v>1050101</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>1040112</v>
+        <v>1050102</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>1040113</v>
+        <v>1050103</v>
       </c>
     </row>
     <row r="103">
@@ -1619,43 +1619,43 @@
         <v>1050001</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>1050101</v>
+        <v>1050104</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1050102</v>
+        <v>1060101</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>1050103</v>
+        <v>1060102</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1050104</v>
+        <v>1060103</v>
       </c>
     </row>
     <row r="107">
@@ -1663,10 +1663,10 @@
         <v>1060001</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>1060101</v>
+        <v>1060104</v>
       </c>
     </row>
     <row r="108">
@@ -1674,10 +1674,10 @@
         <v>1060001</v>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>1060102</v>
+        <v>1060105</v>
       </c>
     </row>
     <row r="109">
@@ -1685,10 +1685,10 @@
         <v>1060001</v>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D109" t="n">
-        <v>1060103</v>
+        <v>1060106</v>
       </c>
     </row>
     <row r="110">
@@ -1696,10 +1696,10 @@
         <v>1060001</v>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
-        <v>1060104</v>
+        <v>1060107</v>
       </c>
     </row>
     <row r="111">
@@ -1707,10 +1707,10 @@
         <v>1060001</v>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D111" t="n">
-        <v>1060105</v>
+        <v>1060108</v>
       </c>
     </row>
     <row r="112">
@@ -1718,43 +1718,43 @@
         <v>1060001</v>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>1060106</v>
+        <v>1060109</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1060107</v>
+        <v>1070101</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>1060108</v>
+        <v>1070102</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C115" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>1060109</v>
+        <v>1070103</v>
       </c>
     </row>
     <row r="116">
@@ -1762,10 +1762,10 @@
         <v>1070001</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>1070101</v>
+        <v>1070104</v>
       </c>
     </row>
     <row r="117">
@@ -1773,10 +1773,10 @@
         <v>1070001</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D117" t="n">
-        <v>1070102</v>
+        <v>1070105</v>
       </c>
     </row>
     <row r="118">
@@ -1784,10 +1784,10 @@
         <v>1070001</v>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D118" t="n">
-        <v>1070103</v>
+        <v>1070106</v>
       </c>
     </row>
     <row r="119">
@@ -1795,10 +1795,10 @@
         <v>1070001</v>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>1070104</v>
+        <v>1070107</v>
       </c>
     </row>
     <row r="120">
@@ -1806,10 +1806,10 @@
         <v>1070001</v>
       </c>
       <c r="C120" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D120" t="n">
-        <v>1070105</v>
+        <v>1070108</v>
       </c>
     </row>
     <row r="121">
@@ -1817,10 +1817,10 @@
         <v>1070001</v>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>1070106</v>
+        <v>1070109</v>
       </c>
     </row>
     <row r="122">
@@ -1828,43 +1828,43 @@
         <v>1070001</v>
       </c>
       <c r="C122" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>1070107</v>
+        <v>1070110</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>1070108</v>
+        <v>1080101</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>1070109</v>
+        <v>1080102</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>1070110</v>
+        <v>1080103</v>
       </c>
     </row>
     <row r="126">
@@ -1872,10 +1872,10 @@
         <v>1080001</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>1080101</v>
+        <v>1080104</v>
       </c>
     </row>
     <row r="127">
@@ -1883,10 +1883,10 @@
         <v>1080001</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D127" t="n">
-        <v>1080102</v>
+        <v>1080105</v>
       </c>
     </row>
     <row r="128">
@@ -1894,10 +1894,10 @@
         <v>1080001</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>1080103</v>
+        <v>1080106</v>
       </c>
     </row>
     <row r="129">
@@ -1905,197 +1905,197 @@
         <v>1080001</v>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>1080104</v>
+        <v>1080107</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>1080105</v>
+        <v>1090102</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>1080106</v>
+        <v>1090103</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C132" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>1080107</v>
+        <v>1090122</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>1090102</v>
+        <v>1090123</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1090103</v>
+        <v>1090124</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1090122</v>
+        <v>1090142</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C136" t="n">
         <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>1090123</v>
+        <v>1090143</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C137" t="n">
         <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>1090124</v>
+        <v>1090144</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>1090142</v>
+        <v>1090162</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C139" t="n">
         <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>1090143</v>
+        <v>1090163</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1090003</v>
+        <v>1090005</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>1090144</v>
+        <v>1090182</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>1090162</v>
+        <v>1090202</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C142" t="n">
         <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>1090163</v>
+        <v>1090203</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>1090182</v>
+        <v>1090204</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1090202</v>
+        <v>1090222</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C145" t="n">
         <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1090203</v>
+        <v>1090223</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C146" t="n">
         <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>1090204</v>
+        <v>1090224</v>
       </c>
     </row>
     <row r="147">
@@ -2103,43 +2103,43 @@
         <v>96</v>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>1090222</v>
+        <v>1090225</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1090223</v>
+        <v>1090242</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>1090224</v>
+        <v>1090243</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>1090225</v>
+        <v>1090244</v>
       </c>
     </row>
     <row r="151">
@@ -2147,54 +2147,54 @@
         <v>1090008</v>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D151" t="n">
-        <v>1090242</v>
+        <v>1090245</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1090008</v>
+        <v>1090009</v>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1090243</v>
+        <v>1090262</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1090244</v>
+        <v>1090282</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>1090245</v>
+        <v>1090283</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1090262</v>
+        <v>1090284</v>
       </c>
     </row>
     <row r="156">
@@ -2202,43 +2202,43 @@
         <v>1090010</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
-        <v>1090282</v>
+        <v>1090285</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1090283</v>
+        <v>1090302</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>1090284</v>
+        <v>1090303</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>1090285</v>
+        <v>1090304</v>
       </c>
     </row>
     <row r="160">
@@ -2246,10 +2246,10 @@
         <v>1090011</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>1090302</v>
+        <v>1090305</v>
       </c>
     </row>
     <row r="161">
@@ -2257,65 +2257,65 @@
         <v>1090011</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D161" t="n">
-        <v>1090303</v>
+        <v>1090306</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1090304</v>
+        <v>1090322</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>1090305</v>
+        <v>1090323</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1090306</v>
+        <v>1100102</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>1090322</v>
+        <v>1100103</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>1090323</v>
+        <v>1100104</v>
       </c>
     </row>
     <row r="167">
@@ -2323,76 +2323,76 @@
         <v>97</v>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>1100102</v>
+        <v>1100105</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>97</v>
+        <v>1100002</v>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>1100103</v>
+        <v>1100122</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>1100104</v>
+        <v>1100142</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170" t="n">
-        <v>1100105</v>
+        <v>1100143</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1100002</v>
+        <v>1100004</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1100122</v>
+        <v>1100162</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>1100142</v>
+        <v>1100163</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1100143</v>
+        <v>1100164</v>
       </c>
     </row>
     <row r="174">
@@ -2400,87 +2400,87 @@
         <v>1100004</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>1100162</v>
+        <v>1100165</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1100004</v>
+        <v>99</v>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>1100163</v>
+        <v>1100182</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1100164</v>
+        <v>1100202</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>1100165</v>
+        <v>1100203</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>99</v>
+        <v>1100006</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>1100182</v>
+        <v>1100204</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1100202</v>
+        <v>1100222</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C180" t="n">
         <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>1100203</v>
+        <v>1100223</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C181" t="n">
         <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>1100204</v>
+        <v>1100224</v>
       </c>
     </row>
     <row r="182">
@@ -2488,43 +2488,43 @@
         <v>1100007</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>1100222</v>
+        <v>1100225</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>1100223</v>
+        <v>1100242</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>1100224</v>
+        <v>1100243</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>1100225</v>
+        <v>1100244</v>
       </c>
     </row>
     <row r="186">
@@ -2532,43 +2532,43 @@
         <v>100</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D186" t="n">
-        <v>1100242</v>
+        <v>1100245</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>1100243</v>
+        <v>1100262</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>1100244</v>
+        <v>1100263</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>1100245</v>
+        <v>1100264</v>
       </c>
     </row>
     <row r="190">
@@ -2576,10 +2576,10 @@
         <v>1100009</v>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D190" t="n">
-        <v>1100262</v>
+        <v>1100265</v>
       </c>
     </row>
     <row r="191">
@@ -2587,43 +2587,43 @@
         <v>1100009</v>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D191" t="n">
-        <v>1100263</v>
+        <v>1100266</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>1100264</v>
+        <v>1100282</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C193" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>1100265</v>
+        <v>1100283</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C194" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>1100266</v>
+        <v>1100284</v>
       </c>
     </row>
     <row r="195">
@@ -2631,10 +2631,10 @@
         <v>1100010</v>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D195" t="n">
-        <v>1100282</v>
+        <v>1100285</v>
       </c>
     </row>
     <row r="196">
@@ -2642,87 +2642,87 @@
         <v>1100010</v>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D196" t="n">
-        <v>1100283</v>
+        <v>1100286</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1100010</v>
+        <v>1100011</v>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>1100284</v>
+        <v>1100302</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>1100285</v>
+        <v>1100322</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C199" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D199" t="n">
-        <v>1100286</v>
+        <v>1100323</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1100011</v>
+        <v>1100012</v>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>1100302</v>
+        <v>1100324</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>1100322</v>
+        <v>1110102</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C202" t="n">
         <v>2</v>
       </c>
       <c r="D202" t="n">
-        <v>1100323</v>
+        <v>1110103</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C203" t="n">
         <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>1100324</v>
+        <v>1110104</v>
       </c>
     </row>
     <row r="204">
@@ -2730,54 +2730,54 @@
         <v>1110001</v>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D204" t="n">
-        <v>1110102</v>
+        <v>1110105</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1110001</v>
+        <v>1110002</v>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>1110103</v>
+        <v>1110122</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>1110104</v>
+        <v>1110142</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C207" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D207" t="n">
-        <v>1110105</v>
+        <v>1110143</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1110002</v>
+        <v>1110003</v>
       </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>1110122</v>
+        <v>1110144</v>
       </c>
     </row>
     <row r="209">
@@ -2785,43 +2785,43 @@
         <v>1110003</v>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
-        <v>1110142</v>
+        <v>1110145</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>1110143</v>
+        <v>1110162</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D211" t="n">
-        <v>1110144</v>
+        <v>1110163</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D212" t="n">
-        <v>1110145</v>
+        <v>1110164</v>
       </c>
     </row>
     <row r="213">
@@ -2829,142 +2829,142 @@
         <v>1110004</v>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>1110162</v>
+        <v>1110165</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>1110163</v>
+        <v>1110182</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D215" t="n">
-        <v>1110164</v>
+        <v>1110183</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>1110165</v>
+        <v>1110184</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1110005</v>
+        <v>1110006</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>1110182</v>
+        <v>1110202</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>1110183</v>
+        <v>1110222</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D219" t="n">
-        <v>1110184</v>
+        <v>1110223</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>1110006</v>
+        <v>1110008</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>1110202</v>
+        <v>1110242</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>102</v>
+        <v>1110009</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>1110222</v>
+        <v>1110262</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>1110223</v>
+        <v>1110282</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1110008</v>
+        <v>1110011</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>1110242</v>
+        <v>1110302</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>1110009</v>
+        <v>1110011</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D224" t="n">
-        <v>1110262</v>
+        <v>1110303</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>103</v>
+        <v>1110011</v>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D225" t="n">
-        <v>1110282</v>
+        <v>1110304</v>
       </c>
     </row>
     <row r="226">
@@ -2972,10 +2972,10 @@
         <v>1110011</v>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D226" t="n">
-        <v>1110302</v>
+        <v>1110305</v>
       </c>
     </row>
     <row r="227">
@@ -2983,98 +2983,98 @@
         <v>1110011</v>
       </c>
       <c r="C227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D227" t="n">
-        <v>1110303</v>
+        <v>1110306</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>1110011</v>
+        <v>104</v>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>1110304</v>
+        <v>1110322</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>1110011</v>
+        <v>1120001</v>
       </c>
       <c r="C229" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>1110305</v>
+        <v>1120102</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>1110011</v>
+        <v>1120001</v>
       </c>
       <c r="C230" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D230" t="n">
-        <v>1110306</v>
+        <v>1120103</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>104</v>
+        <v>1120002</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>1110322</v>
+        <v>1120122</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>1120001</v>
+        <v>1120002</v>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232" t="n">
-        <v>1120102</v>
+        <v>1120123</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" t="n">
-        <v>1120001</v>
+        <v>1120003</v>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>1120103</v>
+        <v>1120142</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" t="n">
-        <v>1120122</v>
+        <v>1120143</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D235" t="n">
-        <v>1120123</v>
+        <v>1120144</v>
       </c>
     </row>
     <row r="236">
@@ -3082,10 +3082,10 @@
         <v>1120003</v>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D236" t="n">
-        <v>1120142</v>
+        <v>1120145</v>
       </c>
     </row>
     <row r="237">
@@ -3093,10 +3093,10 @@
         <v>1120003</v>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D237" t="n">
-        <v>1120143</v>
+        <v>1120146</v>
       </c>
     </row>
     <row r="238">
@@ -3104,10 +3104,10 @@
         <v>1120003</v>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D238" t="n">
-        <v>1120144</v>
+        <v>1120147</v>
       </c>
     </row>
     <row r="239">
@@ -3115,43 +3115,43 @@
         <v>1120003</v>
       </c>
       <c r="C239" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D239" t="n">
-        <v>1120145</v>
+        <v>1120148</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C240" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>1120146</v>
+        <v>1120162</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C241" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>1120147</v>
+        <v>1120163</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C242" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>1120148</v>
+        <v>1120164</v>
       </c>
     </row>
     <row r="243">
@@ -3159,54 +3159,54 @@
         <v>1120004</v>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>1120162</v>
+        <v>1120165</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" t="n">
-        <v>1120004</v>
+        <v>106</v>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>1120163</v>
+        <v>1120182</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" t="n">
-        <v>1120004</v>
+        <v>1120006</v>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>1120164</v>
+        <v>1120202</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" t="n">
-        <v>1120004</v>
+        <v>1120006</v>
       </c>
       <c r="C246" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D246" t="n">
-        <v>1120165</v>
+        <v>1120203</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" t="n">
-        <v>106</v>
+        <v>1120006</v>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D247" t="n">
-        <v>1120182</v>
+        <v>1120204</v>
       </c>
     </row>
     <row r="248">
@@ -3214,43 +3214,43 @@
         <v>1120006</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D248" t="n">
-        <v>1120202</v>
+        <v>1120205</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>1120203</v>
+        <v>1120222</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D250" t="n">
-        <v>1120204</v>
+        <v>1120223</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D251" t="n">
-        <v>1120205</v>
+        <v>1120224</v>
       </c>
     </row>
     <row r="252">
@@ -3258,164 +3258,164 @@
         <v>1120007</v>
       </c>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D252" t="n">
-        <v>1120222</v>
+        <v>1120225</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" t="n">
-        <v>1120007</v>
+        <v>107</v>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>1120223</v>
+        <v>1120242</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" t="n">
-        <v>1120007</v>
+        <v>107</v>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D254" t="n">
-        <v>1120224</v>
+        <v>1120243</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" t="n">
-        <v>1120007</v>
+        <v>108</v>
       </c>
       <c r="C255" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>1120225</v>
+        <v>1120262</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D256" t="n">
-        <v>1120242</v>
+        <v>1120263</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>1120243</v>
+        <v>1120264</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C258" t="n">
         <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>1120262</v>
+        <v>1120282</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C259" t="n">
         <v>2</v>
       </c>
       <c r="D259" t="n">
-        <v>1120263</v>
+        <v>1120283</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C260" t="n">
         <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>1120264</v>
+        <v>1120284</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" t="n">
-        <v>1120010</v>
+        <v>1120011</v>
       </c>
       <c r="C261" t="n">
         <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>1120282</v>
+        <v>1120302</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" t="n">
-        <v>1120010</v>
+        <v>1120012</v>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>1120283</v>
+        <v>1120322</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" t="n">
-        <v>1120010</v>
+        <v>1120012</v>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D263" t="n">
-        <v>1120284</v>
+        <v>1120323</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" t="n">
-        <v>1120011</v>
+        <v>1130001</v>
       </c>
       <c r="C264" t="n">
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>1120302</v>
+        <v>1130102</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" t="n">
-        <v>1120012</v>
+        <v>1130001</v>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D265" t="n">
-        <v>1120322</v>
+        <v>1130103</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" t="n">
-        <v>1120012</v>
+        <v>1130001</v>
       </c>
       <c r="C266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D266" t="n">
-        <v>1120323</v>
+        <v>1130104</v>
       </c>
     </row>
     <row r="267">
@@ -3423,10 +3423,10 @@
         <v>1130001</v>
       </c>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D267" t="n">
-        <v>1130102</v>
+        <v>1130105</v>
       </c>
     </row>
     <row r="268">
@@ -3434,65 +3434,65 @@
         <v>1130001</v>
       </c>
       <c r="C268" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D268" t="n">
-        <v>1130103</v>
+        <v>1130106</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D269" t="n">
-        <v>1130104</v>
+        <v>1130122</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C270" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D270" t="n">
-        <v>1130105</v>
+        <v>1130123</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" t="n">
-        <v>1130001</v>
+        <v>1130003</v>
       </c>
       <c r="C271" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>1130106</v>
+        <v>1130142</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" t="n">
-        <v>1130002</v>
+        <v>1130003</v>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>1130122</v>
+        <v>1130143</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" t="n">
-        <v>1130002</v>
+        <v>1130003</v>
       </c>
       <c r="C273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>1130123</v>
+        <v>1130144</v>
       </c>
     </row>
     <row r="274">
@@ -3500,10 +3500,10 @@
         <v>1130003</v>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>1130142</v>
+        <v>1130145</v>
       </c>
     </row>
     <row r="275">
@@ -3511,43 +3511,43 @@
         <v>1130003</v>
       </c>
       <c r="C275" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D275" t="n">
-        <v>1130143</v>
+        <v>1130146</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>1130144</v>
+        <v>1130162</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C277" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D277" t="n">
-        <v>1130145</v>
+        <v>1130163</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C278" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D278" t="n">
-        <v>1130146</v>
+        <v>1130164</v>
       </c>
     </row>
     <row r="279">
@@ -3555,10 +3555,10 @@
         <v>1130004</v>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D279" t="n">
-        <v>1130162</v>
+        <v>1130165</v>
       </c>
     </row>
     <row r="280">
@@ -3566,10 +3566,10 @@
         <v>1130004</v>
       </c>
       <c r="C280" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D280" t="n">
-        <v>1130163</v>
+        <v>1130166</v>
       </c>
     </row>
     <row r="281">
@@ -3577,10 +3577,10 @@
         <v>1130004</v>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D281" t="n">
-        <v>1130164</v>
+        <v>1130167</v>
       </c>
     </row>
     <row r="282">
@@ -3588,10 +3588,10 @@
         <v>1130004</v>
       </c>
       <c r="C282" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D282" t="n">
-        <v>1130165</v>
+        <v>1130168</v>
       </c>
     </row>
     <row r="283">
@@ -3599,43 +3599,43 @@
         <v>1130004</v>
       </c>
       <c r="C283" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D283" t="n">
-        <v>1130166</v>
+        <v>1130169</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C284" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>1130167</v>
+        <v>1130182</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C285" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D285" t="n">
-        <v>1130168</v>
+        <v>1130183</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C286" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D286" t="n">
-        <v>1130169</v>
+        <v>1130184</v>
       </c>
     </row>
     <row r="287">
@@ -3643,10 +3643,10 @@
         <v>1130005</v>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D287" t="n">
-        <v>1130182</v>
+        <v>1130185</v>
       </c>
     </row>
     <row r="288">
@@ -3654,10 +3654,10 @@
         <v>1130005</v>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D288" t="n">
-        <v>1130183</v>
+        <v>1130186</v>
       </c>
     </row>
     <row r="289">
@@ -3665,10 +3665,10 @@
         <v>1130005</v>
       </c>
       <c r="C289" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D289" t="n">
-        <v>1130184</v>
+        <v>1130187</v>
       </c>
     </row>
     <row r="290">
@@ -3676,87 +3676,87 @@
         <v>1130005</v>
       </c>
       <c r="C290" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D290" t="n">
-        <v>1130185</v>
+        <v>1130188</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C291" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>1130186</v>
+        <v>1130202</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C292" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D292" t="n">
-        <v>1130187</v>
+        <v>1130203</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C293" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D293" t="n">
-        <v>1130188</v>
+        <v>1130204</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" t="n">
-        <v>1130006</v>
+        <v>1130007</v>
       </c>
       <c r="C294" t="n">
         <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>1130202</v>
+        <v>1130222</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" t="n">
-        <v>1130006</v>
+        <v>1130008</v>
       </c>
       <c r="C295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>1130203</v>
+        <v>1130242</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" t="n">
-        <v>1130006</v>
+        <v>1130008</v>
       </c>
       <c r="C296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D296" t="n">
-        <v>1130204</v>
+        <v>1130243</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" t="n">
-        <v>1130007</v>
+        <v>1130008</v>
       </c>
       <c r="C297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D297" t="n">
-        <v>1130222</v>
+        <v>1130244</v>
       </c>
     </row>
     <row r="298">
@@ -3764,10 +3764,10 @@
         <v>1130008</v>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D298" t="n">
-        <v>1130242</v>
+        <v>1130245</v>
       </c>
     </row>
     <row r="299">
@@ -3775,54 +3775,54 @@
         <v>1130008</v>
       </c>
       <c r="C299" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D299" t="n">
-        <v>1130243</v>
+        <v>1130246</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" t="n">
-        <v>1130008</v>
+        <v>1130009</v>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D300" t="n">
-        <v>1130244</v>
+        <v>1130262</v>
       </c>
     </row>
     <row r="301">
       <c r="B301" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C301" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>1130245</v>
+        <v>1130282</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C302" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D302" t="n">
-        <v>1130246</v>
+        <v>1130283</v>
       </c>
     </row>
     <row r="303">
       <c r="B303" t="n">
-        <v>1130009</v>
+        <v>1130010</v>
       </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D303" t="n">
-        <v>1130262</v>
+        <v>1130284</v>
       </c>
     </row>
     <row r="304">
@@ -3830,10 +3830,10 @@
         <v>1130010</v>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D304" t="n">
-        <v>1130282</v>
+        <v>1130285</v>
       </c>
     </row>
     <row r="305">
@@ -3841,10 +3841,10 @@
         <v>1130010</v>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D305" t="n">
-        <v>1130283</v>
+        <v>1130286</v>
       </c>
     </row>
     <row r="306">
@@ -3852,10 +3852,10 @@
         <v>1130010</v>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D306" t="n">
-        <v>1130284</v>
+        <v>1130287</v>
       </c>
     </row>
     <row r="307">
@@ -3863,10 +3863,10 @@
         <v>1130010</v>
       </c>
       <c r="C307" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D307" t="n">
-        <v>1130285</v>
+        <v>1130288</v>
       </c>
     </row>
     <row r="308">
@@ -3874,10 +3874,10 @@
         <v>1130010</v>
       </c>
       <c r="C308" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D308" t="n">
-        <v>1130286</v>
+        <v>1130289</v>
       </c>
     </row>
     <row r="309">
@@ -3885,43 +3885,43 @@
         <v>1130010</v>
       </c>
       <c r="C309" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D309" t="n">
-        <v>1130287</v>
+        <v>1130290</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C310" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>1130288</v>
+        <v>1130302</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C311" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D311" t="n">
-        <v>1130289</v>
+        <v>1130303</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C312" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D312" t="n">
-        <v>1130290</v>
+        <v>1130304</v>
       </c>
     </row>
     <row r="313">
@@ -3929,10 +3929,10 @@
         <v>1130011</v>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D313" t="n">
-        <v>1130302</v>
+        <v>1130305</v>
       </c>
     </row>
     <row r="314">
@@ -3940,10 +3940,10 @@
         <v>1130011</v>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D314" t="n">
-        <v>1130303</v>
+        <v>1130306</v>
       </c>
     </row>
     <row r="315">
@@ -3951,43 +3951,43 @@
         <v>1130011</v>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D315" t="n">
-        <v>1130304</v>
+        <v>1130307</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>1130305</v>
+        <v>1130322</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C317" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D317" t="n">
-        <v>1130306</v>
+        <v>1130323</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C318" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D318" t="n">
-        <v>1130307</v>
+        <v>1130324</v>
       </c>
     </row>
     <row r="319">
@@ -3995,10 +3995,10 @@
         <v>1130012</v>
       </c>
       <c r="C319" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D319" t="n">
-        <v>1130322</v>
+        <v>1130325</v>
       </c>
     </row>
     <row r="320">
@@ -4006,43 +4006,428 @@
         <v>1130012</v>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D320" t="n">
-        <v>1130323</v>
+        <v>1130326</v>
       </c>
     </row>
     <row r="321">
       <c r="B321" t="n">
-        <v>1130012</v>
+        <v>1140001</v>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D321" t="n">
-        <v>1130324</v>
+        <v>1140102</v>
       </c>
     </row>
     <row r="322">
       <c r="B322" t="n">
-        <v>1130012</v>
+        <v>1140002</v>
       </c>
       <c r="C322" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D322" t="n">
-        <v>1130325</v>
+        <v>1140122</v>
       </c>
     </row>
     <row r="323">
       <c r="B323" t="n">
-        <v>1130012</v>
+        <v>1140002</v>
       </c>
       <c r="C323" t="n">
+        <v>2</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1140123</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C324" t="n">
+        <v>3</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1140124</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C325" t="n">
+        <v>4</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1140125</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1</v>
+      </c>
+      <c r="D326" t="n">
+        <v>1140142</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C327" t="n">
+        <v>2</v>
+      </c>
+      <c r="D327" t="n">
+        <v>1140143</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C328" t="n">
+        <v>3</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1140144</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C329" t="n">
+        <v>4</v>
+      </c>
+      <c r="D329" t="n">
+        <v>1140145</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1140162</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C331" t="n">
+        <v>2</v>
+      </c>
+      <c r="D331" t="n">
+        <v>1140163</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C332" t="n">
+        <v>3</v>
+      </c>
+      <c r="D332" t="n">
+        <v>1140164</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C333" t="n">
+        <v>4</v>
+      </c>
+      <c r="D333" t="n">
+        <v>1140165</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1140182</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C335" t="n">
+        <v>2</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1140183</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C336" t="n">
+        <v>3</v>
+      </c>
+      <c r="D336" t="n">
+        <v>1140184</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C337" t="n">
+        <v>4</v>
+      </c>
+      <c r="D337" t="n">
+        <v>1140185</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1</v>
+      </c>
+      <c r="D338" t="n">
+        <v>1140202</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C339" t="n">
+        <v>2</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1140203</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C340" t="n">
+        <v>3</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1140204</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C341" t="n">
+        <v>4</v>
+      </c>
+      <c r="D341" t="n">
+        <v>1140205</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1</v>
+      </c>
+      <c r="D342" t="n">
+        <v>1140222</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C343" t="n">
+        <v>2</v>
+      </c>
+      <c r="D343" t="n">
+        <v>1140223</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C344" t="n">
+        <v>3</v>
+      </c>
+      <c r="D344" t="n">
+        <v>1140224</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C345" t="n">
+        <v>4</v>
+      </c>
+      <c r="D345" t="n">
+        <v>1140225</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C346" t="n">
+        <v>1</v>
+      </c>
+      <c r="D346" t="n">
+        <v>1140242</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C347" t="n">
+        <v>2</v>
+      </c>
+      <c r="D347" t="n">
+        <v>1140243</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1140262</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C349" t="n">
+        <v>2</v>
+      </c>
+      <c r="D349" t="n">
+        <v>1140263</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C350" t="n">
+        <v>1</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1140282</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C351" t="n">
+        <v>2</v>
+      </c>
+      <c r="D351" t="n">
+        <v>1140283</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>110</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1</v>
+      </c>
+      <c r="D352" t="n">
+        <v>1140302</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>110</v>
+      </c>
+      <c r="C353" t="n">
+        <v>2</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1140303</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1140322</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C355" t="n">
+        <v>2</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1140323</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C356" t="n">
+        <v>3</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1140324</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C357" t="n">
+        <v>4</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1140325</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C358" t="n">
         <v>5</v>
       </c>
-      <c r="D323" t="n">
-        <v>1130326</v>
+      <c r="D358" t="n">
+        <v>1140326</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J358"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,57 +769,57 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11062</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>11060</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>11063</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C29" t="n">
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>11061</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C30" t="n">
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>11059</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="31">
@@ -827,10 +827,10 @@
         <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>11012</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="32">
@@ -838,10 +838,10 @@
         <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>11019</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="33">
@@ -849,10 +849,10 @@
         <v>98</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>11017</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="34">
@@ -860,65 +860,65 @@
         <v>98</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>11016</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>11014</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>11020</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>11018</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>11015</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>11013</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="40">
@@ -926,10 +926,10 @@
         <v>980001</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>980101</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="41">
@@ -937,10 +937,10 @@
         <v>980001</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>980102</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="42">
@@ -948,10 +948,10 @@
         <v>980001</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>980103</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="43">
@@ -959,10 +959,10 @@
         <v>980001</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>980104</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="44">
@@ -970,10 +970,10 @@
         <v>980001</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>980105</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="45">
@@ -981,10 +981,10 @@
         <v>980001</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>980106</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="46">
@@ -992,10 +992,10 @@
         <v>980001</v>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>980107</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="47">
@@ -1003,10 +1003,10 @@
         <v>980001</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>980108</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="48">
@@ -1014,65 +1014,65 @@
         <v>980001</v>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>980109</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>980110</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>980111</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>980112</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C52" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>980113</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C53" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>980114</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="54">
@@ -1080,10 +1080,10 @@
         <v>990001</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>990101</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="55">
@@ -1091,10 +1091,10 @@
         <v>990001</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>990102</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="56">
@@ -1102,65 +1102,65 @@
         <v>990001</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>990103</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>990104</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>990105</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>990106</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>990107</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>990108</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="62">
@@ -1168,10 +1168,10 @@
         <v>1000001</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>1000101</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="63">
@@ -1179,109 +1179,109 @@
         <v>1000001</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>1000102</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1000103</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>1000104</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>1000105</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>1000106</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1000109</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>1010101</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>1010102</v>
+        <v>1020103</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>1010103</v>
+        <v>1020104</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>1010104</v>
+        <v>1020105</v>
       </c>
     </row>
     <row r="73">
@@ -1289,10 +1289,10 @@
         <v>1020001</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>1020101</v>
+        <v>1020106</v>
       </c>
     </row>
     <row r="74">
@@ -1300,10 +1300,10 @@
         <v>1020001</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>1020102</v>
+        <v>1020107</v>
       </c>
     </row>
     <row r="75">
@@ -1311,10 +1311,10 @@
         <v>1020001</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D75" t="n">
-        <v>1020103</v>
+        <v>1020108</v>
       </c>
     </row>
     <row r="76">
@@ -1322,65 +1322,65 @@
         <v>1020001</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>1020104</v>
+        <v>1020109</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1020105</v>
+        <v>1030101</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>1020106</v>
+        <v>1030102</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>1020107</v>
+        <v>1030103</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>1020108</v>
+        <v>1030104</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>1020109</v>
+        <v>1030105</v>
       </c>
     </row>
     <row r="82">
@@ -1388,10 +1388,10 @@
         <v>1030001</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>1030101</v>
+        <v>1030106</v>
       </c>
     </row>
     <row r="83">
@@ -1399,10 +1399,10 @@
         <v>1030001</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>1030102</v>
+        <v>1030108</v>
       </c>
     </row>
     <row r="84">
@@ -1410,65 +1410,65 @@
         <v>1030001</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D84" t="n">
-        <v>1030103</v>
+        <v>1030109</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1030104</v>
+        <v>1040101</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>1030105</v>
+        <v>1040102</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1030106</v>
+        <v>1040103</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>1030108</v>
+        <v>1040104</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>1030109</v>
+        <v>1040105</v>
       </c>
     </row>
     <row r="90">
@@ -1476,10 +1476,10 @@
         <v>1040001</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>1040101</v>
+        <v>1040106</v>
       </c>
     </row>
     <row r="91">
@@ -1487,10 +1487,10 @@
         <v>1040001</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>1040102</v>
+        <v>1040107</v>
       </c>
     </row>
     <row r="92">
@@ -1498,10 +1498,10 @@
         <v>1040001</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D92" t="n">
-        <v>1040103</v>
+        <v>1040108</v>
       </c>
     </row>
     <row r="93">
@@ -1509,10 +1509,10 @@
         <v>1040001</v>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>1040104</v>
+        <v>1040112</v>
       </c>
     </row>
     <row r="94">
@@ -1520,109 +1520,109 @@
         <v>1040001</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>1040105</v>
+        <v>1040113</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1040106</v>
+        <v>1050101</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>1040107</v>
+        <v>1050102</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>1040108</v>
+        <v>1050103</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>1040112</v>
+        <v>1050104</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1040113</v>
+        <v>1060101</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>1050101</v>
+        <v>1060102</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>1050102</v>
+        <v>1060103</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>1050103</v>
+        <v>1060104</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>1050104</v>
+        <v>1060105</v>
       </c>
     </row>
     <row r="104">
@@ -1630,10 +1630,10 @@
         <v>1060001</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>1060101</v>
+        <v>1060106</v>
       </c>
     </row>
     <row r="105">
@@ -1641,10 +1641,10 @@
         <v>1060001</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>1060102</v>
+        <v>1060107</v>
       </c>
     </row>
     <row r="106">
@@ -1652,10 +1652,10 @@
         <v>1060001</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
-        <v>1060103</v>
+        <v>1060108</v>
       </c>
     </row>
     <row r="107">
@@ -1663,65 +1663,65 @@
         <v>1060001</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>1060104</v>
+        <v>1060109</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>1060105</v>
+        <v>1070101</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>1060106</v>
+        <v>1070102</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>1060107</v>
+        <v>1070103</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>1060108</v>
+        <v>1070104</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
-        <v>1060109</v>
+        <v>1070105</v>
       </c>
     </row>
     <row r="113">
@@ -1729,10 +1729,10 @@
         <v>1070001</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D113" t="n">
-        <v>1070101</v>
+        <v>1070106</v>
       </c>
     </row>
     <row r="114">
@@ -1740,10 +1740,10 @@
         <v>1070001</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D114" t="n">
-        <v>1070102</v>
+        <v>1070107</v>
       </c>
     </row>
     <row r="115">
@@ -1751,10 +1751,10 @@
         <v>1070001</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D115" t="n">
-        <v>1070103</v>
+        <v>1070108</v>
       </c>
     </row>
     <row r="116">
@@ -1762,10 +1762,10 @@
         <v>1070001</v>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D116" t="n">
-        <v>1070104</v>
+        <v>1070109</v>
       </c>
     </row>
     <row r="117">
@@ -1773,65 +1773,65 @@
         <v>1070001</v>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D117" t="n">
-        <v>1070105</v>
+        <v>1070110</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>1070106</v>
+        <v>1080101</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C119" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>1070107</v>
+        <v>1080102</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>1070108</v>
+        <v>1080103</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>1070109</v>
+        <v>1080104</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D122" t="n">
-        <v>1070110</v>
+        <v>1080105</v>
       </c>
     </row>
     <row r="123">
@@ -1839,10 +1839,10 @@
         <v>1080001</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>1080101</v>
+        <v>1080106</v>
       </c>
     </row>
     <row r="124">
@@ -1850,1198 +1850,1198 @@
         <v>1080001</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
-        <v>1080102</v>
+        <v>1080107</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>1080103</v>
+        <v>1090102</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>1080104</v>
+        <v>1090103</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>1080105</v>
+        <v>1090122</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>1080106</v>
+        <v>1090123</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C129" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>1080107</v>
+        <v>1090124</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>1090102</v>
+        <v>1090142</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C131" t="n">
         <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>1090103</v>
+        <v>1090143</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>1090122</v>
+        <v>1090144</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>1090123</v>
+        <v>1090162</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>1090124</v>
+        <v>1090163</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1090003</v>
+        <v>1090005</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1090142</v>
+        <v>1090182</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>1090143</v>
+        <v>1090202</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>1090144</v>
+        <v>1090203</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>1090162</v>
+        <v>1090204</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>1090163</v>
+        <v>1090222</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>1090182</v>
+        <v>1090223</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>1090202</v>
+        <v>1090224</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>1090203</v>
+        <v>1090225</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>1090204</v>
+        <v>1090242</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>1090222</v>
+        <v>1090243</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>1090223</v>
+        <v>1090244</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D146" t="n">
-        <v>1090224</v>
+        <v>1090245</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>96</v>
+        <v>1090009</v>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1090225</v>
+        <v>1090262</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1090242</v>
+        <v>1090282</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C149" t="n">
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>1090243</v>
+        <v>1090283</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C150" t="n">
         <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>1090244</v>
+        <v>1090284</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C151" t="n">
         <v>4</v>
       </c>
       <c r="D151" t="n">
-        <v>1090245</v>
+        <v>1090285</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1090009</v>
+        <v>1090011</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1090262</v>
+        <v>1090302</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>1090282</v>
+        <v>1090303</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>1090283</v>
+        <v>1090304</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>1090284</v>
+        <v>1090305</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D156" t="n">
-        <v>1090285</v>
+        <v>1090306</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1090302</v>
+        <v>1090322</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C158" t="n">
         <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>1090303</v>
+        <v>1090323</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>1090304</v>
+        <v>1100102</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>1090305</v>
+        <v>1100103</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>1090306</v>
+        <v>1100104</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>1090322</v>
+        <v>1100105</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1090012</v>
+        <v>1100002</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>1090323</v>
+        <v>1100122</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1100102</v>
+        <v>1100142</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C165" t="n">
         <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>1100103</v>
+        <v>1100143</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>1100104</v>
+        <v>1100162</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D167" t="n">
-        <v>1100105</v>
+        <v>1100163</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1100002</v>
+        <v>1100004</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>1100122</v>
+        <v>1100164</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>1100142</v>
+        <v>1100165</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1100003</v>
+        <v>99</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>1100143</v>
+        <v>1100182</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1100162</v>
+        <v>1100202</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C172" t="n">
         <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>1100163</v>
+        <v>1100203</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C173" t="n">
         <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1100164</v>
+        <v>1100204</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C174" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1100165</v>
+        <v>1100222</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>99</v>
+        <v>1100007</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>1100182</v>
+        <v>1100223</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>1100202</v>
+        <v>1100224</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>1100203</v>
+        <v>1100225</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>1100006</v>
+        <v>100</v>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1100204</v>
+        <v>1100242</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>1100222</v>
+        <v>1100243</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D180" t="n">
-        <v>1100223</v>
+        <v>1100244</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>1100224</v>
+        <v>1100245</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1100007</v>
+        <v>1100009</v>
       </c>
       <c r="C182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1100225</v>
+        <v>1100262</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>1100242</v>
+        <v>1100263</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>1100243</v>
+        <v>1100264</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>1100244</v>
+        <v>1100265</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D186" t="n">
-        <v>1100245</v>
+        <v>1100266</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>1100262</v>
+        <v>1100282</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C188" t="n">
         <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>1100263</v>
+        <v>1100283</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C189" t="n">
         <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>1100264</v>
+        <v>1100284</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C190" t="n">
         <v>4</v>
       </c>
       <c r="D190" t="n">
-        <v>1100265</v>
+        <v>1100285</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C191" t="n">
         <v>5</v>
       </c>
       <c r="D191" t="n">
-        <v>1100266</v>
+        <v>1100286</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1100010</v>
+        <v>1100011</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>1100282</v>
+        <v>1100302</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>1100283</v>
+        <v>1100322</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D194" t="n">
-        <v>1100284</v>
+        <v>1100323</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>1100285</v>
+        <v>1100324</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C196" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>1100286</v>
+        <v>1110102</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1100011</v>
+        <v>1110001</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>1100302</v>
+        <v>1110103</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>1100322</v>
+        <v>1110104</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D199" t="n">
-        <v>1100323</v>
+        <v>1110105</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1100012</v>
+        <v>1110002</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>1100324</v>
+        <v>1110122</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>1110102</v>
+        <v>1110142</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C202" t="n">
         <v>2</v>
       </c>
       <c r="D202" t="n">
-        <v>1110103</v>
+        <v>1110143</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C203" t="n">
         <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>1110104</v>
+        <v>1110144</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1110001</v>
+        <v>1110003</v>
       </c>
       <c r="C204" t="n">
         <v>4</v>
       </c>
       <c r="D204" t="n">
-        <v>1110105</v>
+        <v>1110145</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1110002</v>
+        <v>1110004</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>1110122</v>
+        <v>1110162</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" t="n">
-        <v>1110142</v>
+        <v>1110163</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>1110143</v>
+        <v>1110164</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D208" t="n">
-        <v>1110144</v>
+        <v>1110165</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1110003</v>
+        <v>1110005</v>
       </c>
       <c r="C209" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>1110145</v>
+        <v>1110182</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D210" t="n">
-        <v>1110162</v>
+        <v>1110183</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>1110163</v>
+        <v>1110184</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1110004</v>
+        <v>1110006</v>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>1110164</v>
+        <v>1110202</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C213" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>1110165</v>
+        <v>1110222</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D214" t="n">
-        <v>1110182</v>
+        <v>1110223</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1110005</v>
+        <v>1110008</v>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>1110183</v>
+        <v>1110242</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1110005</v>
+        <v>1110009</v>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>1110184</v>
+        <v>1110262</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1110006</v>
+        <v>103</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>1110202</v>
+        <v>1110282</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>102</v>
+        <v>1110011</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>1110222</v>
+        <v>1110302</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>102</v>
+        <v>1110011</v>
       </c>
       <c r="C219" t="n">
         <v>2</v>
       </c>
       <c r="D219" t="n">
-        <v>1110223</v>
+        <v>1110303</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>1110008</v>
+        <v>1110011</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>1110242</v>
+        <v>1110304</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>1110009</v>
+        <v>1110011</v>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D221" t="n">
-        <v>1110262</v>
+        <v>1110305</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>103</v>
+        <v>1110011</v>
       </c>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D222" t="n">
-        <v>1110282</v>
+        <v>1110306</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1110011</v>
+        <v>104</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>1110302</v>
+        <v>1110322</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>1110011</v>
+        <v>1120001</v>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>1110303</v>
+        <v>1120102</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>1110011</v>
+        <v>1120001</v>
       </c>
       <c r="C225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D225" t="n">
-        <v>1110304</v>
+        <v>1120103</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>1110011</v>
+        <v>1120002</v>
       </c>
       <c r="C226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>1110305</v>
+        <v>1120122</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>1110011</v>
+        <v>1120002</v>
       </c>
       <c r="C227" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D227" t="n">
-        <v>1110306</v>
+        <v>1120123</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>104</v>
+        <v>1120003</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>1110322</v>
+        <v>1120142</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>1120001</v>
+        <v>1120003</v>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="n">
-        <v>1120102</v>
+        <v>1120143</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>1120001</v>
+        <v>1120003</v>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>1120103</v>
+        <v>1120144</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D231" t="n">
-        <v>1120122</v>
+        <v>1120145</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D232" t="n">
-        <v>1120123</v>
+        <v>1120146</v>
       </c>
     </row>
     <row r="233">
@@ -3049,10 +3049,10 @@
         <v>1120003</v>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D233" t="n">
-        <v>1120142</v>
+        <v>1120147</v>
       </c>
     </row>
     <row r="234">
@@ -3060,461 +3060,461 @@
         <v>1120003</v>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D234" t="n">
-        <v>1120143</v>
+        <v>1120148</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>1120144</v>
+        <v>1120162</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D236" t="n">
-        <v>1120145</v>
+        <v>1120163</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C237" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>1120146</v>
+        <v>1120164</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C238" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D238" t="n">
-        <v>1120147</v>
+        <v>1120165</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" t="n">
-        <v>1120003</v>
+        <v>106</v>
       </c>
       <c r="C239" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>1120148</v>
+        <v>1120182</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" t="n">
-        <v>1120004</v>
+        <v>1120006</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>1120162</v>
+        <v>1120202</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" t="n">
-        <v>1120004</v>
+        <v>1120006</v>
       </c>
       <c r="C241" t="n">
         <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>1120163</v>
+        <v>1120203</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" t="n">
-        <v>1120004</v>
+        <v>1120006</v>
       </c>
       <c r="C242" t="n">
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>1120164</v>
+        <v>1120204</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" t="n">
-        <v>1120004</v>
+        <v>1120006</v>
       </c>
       <c r="C243" t="n">
         <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>1120165</v>
+        <v>1120205</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" t="n">
-        <v>106</v>
+        <v>1120007</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>1120182</v>
+        <v>1120222</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245" t="n">
-        <v>1120202</v>
+        <v>1120223</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D246" t="n">
-        <v>1120203</v>
+        <v>1120224</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D247" t="n">
-        <v>1120204</v>
+        <v>1120225</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" t="n">
-        <v>1120006</v>
+        <v>107</v>
       </c>
       <c r="C248" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>1120205</v>
+        <v>1120242</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" t="n">
-        <v>1120007</v>
+        <v>107</v>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" t="n">
-        <v>1120222</v>
+        <v>1120243</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" t="n">
-        <v>1120007</v>
+        <v>108</v>
       </c>
       <c r="C250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>1120223</v>
+        <v>1120262</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" t="n">
-        <v>1120007</v>
+        <v>108</v>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D251" t="n">
-        <v>1120224</v>
+        <v>1120263</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" t="n">
-        <v>1120007</v>
+        <v>108</v>
       </c>
       <c r="C252" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D252" t="n">
-        <v>1120225</v>
+        <v>1120264</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" t="n">
-        <v>107</v>
+        <v>1120010</v>
       </c>
       <c r="C253" t="n">
         <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>1120242</v>
+        <v>1120282</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" t="n">
-        <v>107</v>
+        <v>1120010</v>
       </c>
       <c r="C254" t="n">
         <v>2</v>
       </c>
       <c r="D254" t="n">
-        <v>1120243</v>
+        <v>1120283</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D255" t="n">
-        <v>1120262</v>
+        <v>1120284</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" t="n">
-        <v>108</v>
+        <v>1120011</v>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>1120263</v>
+        <v>1120302</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" t="n">
-        <v>108</v>
+        <v>1120012</v>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>1120264</v>
+        <v>1120322</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" t="n">
-        <v>1120010</v>
+        <v>1120012</v>
       </c>
       <c r="C258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D258" t="n">
-        <v>1120282</v>
+        <v>1120323</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" t="n">
-        <v>1120010</v>
+        <v>1130001</v>
       </c>
       <c r="C259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>1120283</v>
+        <v>1130102</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" t="n">
-        <v>1120010</v>
+        <v>1130001</v>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D260" t="n">
-        <v>1120284</v>
+        <v>1130103</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" t="n">
-        <v>1120011</v>
+        <v>1130001</v>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D261" t="n">
-        <v>1120302</v>
+        <v>1130104</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" t="n">
-        <v>1120012</v>
+        <v>1130001</v>
       </c>
       <c r="C262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D262" t="n">
-        <v>1120322</v>
+        <v>1130105</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" t="n">
-        <v>1120012</v>
+        <v>1130001</v>
       </c>
       <c r="C263" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D263" t="n">
-        <v>1120323</v>
+        <v>1130106</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C264" t="n">
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>1130102</v>
+        <v>1130122</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C265" t="n">
         <v>2</v>
       </c>
       <c r="D265" t="n">
-        <v>1130103</v>
+        <v>1130123</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" t="n">
-        <v>1130001</v>
+        <v>1130003</v>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>1130104</v>
+        <v>1130142</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" t="n">
-        <v>1130001</v>
+        <v>1130003</v>
       </c>
       <c r="C267" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D267" t="n">
-        <v>1130105</v>
+        <v>1130143</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" t="n">
-        <v>1130001</v>
+        <v>1130003</v>
       </c>
       <c r="C268" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>1130106</v>
+        <v>1130144</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" t="n">
-        <v>1130002</v>
+        <v>1130003</v>
       </c>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D269" t="n">
-        <v>1130122</v>
+        <v>1130145</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" t="n">
-        <v>1130002</v>
+        <v>1130003</v>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D270" t="n">
-        <v>1130123</v>
+        <v>1130146</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C271" t="n">
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>1130142</v>
+        <v>1130162</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C272" t="n">
         <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>1130143</v>
+        <v>1130163</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C273" t="n">
         <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>1130144</v>
+        <v>1130164</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C274" t="n">
         <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>1130145</v>
+        <v>1130165</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C275" t="n">
         <v>5</v>
       </c>
       <c r="D275" t="n">
-        <v>1130146</v>
+        <v>1130166</v>
       </c>
     </row>
     <row r="276">
@@ -3522,10 +3522,10 @@
         <v>1130004</v>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D276" t="n">
-        <v>1130162</v>
+        <v>1130167</v>
       </c>
     </row>
     <row r="277">
@@ -3533,10 +3533,10 @@
         <v>1130004</v>
       </c>
       <c r="C277" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D277" t="n">
-        <v>1130163</v>
+        <v>1130168</v>
       </c>
     </row>
     <row r="278">
@@ -3544,65 +3544,65 @@
         <v>1130004</v>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D278" t="n">
-        <v>1130164</v>
+        <v>1130169</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C279" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>1130165</v>
+        <v>1130182</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C280" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D280" t="n">
-        <v>1130166</v>
+        <v>1130183</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C281" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D281" t="n">
-        <v>1130167</v>
+        <v>1130184</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C282" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D282" t="n">
-        <v>1130168</v>
+        <v>1130185</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C283" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D283" t="n">
-        <v>1130169</v>
+        <v>1130186</v>
       </c>
     </row>
     <row r="284">
@@ -3610,10 +3610,10 @@
         <v>1130005</v>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D284" t="n">
-        <v>1130182</v>
+        <v>1130187</v>
       </c>
     </row>
     <row r="285">
@@ -3621,175 +3621,175 @@
         <v>1130005</v>
       </c>
       <c r="C285" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D285" t="n">
-        <v>1130183</v>
+        <v>1130188</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C286" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>1130184</v>
+        <v>1130202</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C287" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D287" t="n">
-        <v>1130185</v>
+        <v>1130203</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C288" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D288" t="n">
-        <v>1130186</v>
+        <v>1130204</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" t="n">
-        <v>1130005</v>
+        <v>1130007</v>
       </c>
       <c r="C289" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>1130187</v>
+        <v>1130222</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" t="n">
-        <v>1130005</v>
+        <v>1130008</v>
       </c>
       <c r="C290" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>1130188</v>
+        <v>1130242</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" t="n">
-        <v>1130006</v>
+        <v>1130008</v>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D291" t="n">
-        <v>1130202</v>
+        <v>1130243</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" t="n">
-        <v>1130006</v>
+        <v>1130008</v>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D292" t="n">
-        <v>1130203</v>
+        <v>1130244</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" t="n">
-        <v>1130006</v>
+        <v>1130008</v>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D293" t="n">
-        <v>1130204</v>
+        <v>1130245</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" t="n">
-        <v>1130007</v>
+        <v>1130008</v>
       </c>
       <c r="C294" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D294" t="n">
-        <v>1130222</v>
+        <v>1130246</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" t="n">
-        <v>1130008</v>
+        <v>1130009</v>
       </c>
       <c r="C295" t="n">
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>1130242</v>
+        <v>1130262</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>1130243</v>
+        <v>1130282</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D297" t="n">
-        <v>1130244</v>
+        <v>1130283</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D298" t="n">
-        <v>1130245</v>
+        <v>1130284</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C299" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D299" t="n">
-        <v>1130246</v>
+        <v>1130285</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" t="n">
-        <v>1130009</v>
+        <v>1130010</v>
       </c>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D300" t="n">
-        <v>1130262</v>
+        <v>1130286</v>
       </c>
     </row>
     <row r="301">
@@ -3797,10 +3797,10 @@
         <v>1130010</v>
       </c>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D301" t="n">
-        <v>1130282</v>
+        <v>1130287</v>
       </c>
     </row>
     <row r="302">
@@ -3808,10 +3808,10 @@
         <v>1130010</v>
       </c>
       <c r="C302" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D302" t="n">
-        <v>1130283</v>
+        <v>1130288</v>
       </c>
     </row>
     <row r="303">
@@ -3819,10 +3819,10 @@
         <v>1130010</v>
       </c>
       <c r="C303" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D303" t="n">
-        <v>1130284</v>
+        <v>1130289</v>
       </c>
     </row>
     <row r="304">
@@ -3830,65 +3830,65 @@
         <v>1130010</v>
       </c>
       <c r="C304" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D304" t="n">
-        <v>1130285</v>
+        <v>1130290</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D305" t="n">
-        <v>1130286</v>
+        <v>1130302</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C306" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D306" t="n">
-        <v>1130287</v>
+        <v>1130303</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C307" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D307" t="n">
-        <v>1130288</v>
+        <v>1130304</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C308" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D308" t="n">
-        <v>1130289</v>
+        <v>1130305</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C309" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D309" t="n">
-        <v>1130290</v>
+        <v>1130306</v>
       </c>
     </row>
     <row r="310">
@@ -3896,538 +3896,560 @@
         <v>1130011</v>
       </c>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D310" t="n">
-        <v>1130302</v>
+        <v>1130307</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>1130303</v>
+        <v>1130322</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D312" t="n">
-        <v>1130304</v>
+        <v>1130323</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C313" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D313" t="n">
-        <v>1130305</v>
+        <v>1130324</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C314" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D314" t="n">
-        <v>1130306</v>
+        <v>1130325</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C315" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D315" t="n">
-        <v>1130307</v>
+        <v>1130326</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" t="n">
-        <v>1130012</v>
+        <v>1140001</v>
       </c>
       <c r="C316" t="n">
         <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>1130322</v>
+        <v>1140102</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" t="n">
-        <v>1130012</v>
+        <v>1140002</v>
       </c>
       <c r="C317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D317" t="n">
-        <v>1130323</v>
+        <v>1140122</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" t="n">
-        <v>1130012</v>
+        <v>1140002</v>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D318" t="n">
-        <v>1130324</v>
+        <v>1140123</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" t="n">
-        <v>1130012</v>
+        <v>1140002</v>
       </c>
       <c r="C319" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D319" t="n">
-        <v>1130325</v>
+        <v>1140124</v>
       </c>
     </row>
     <row r="320">
       <c r="B320" t="n">
-        <v>1130012</v>
+        <v>1140002</v>
       </c>
       <c r="C320" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D320" t="n">
-        <v>1130326</v>
+        <v>1140125</v>
       </c>
     </row>
     <row r="321">
       <c r="B321" t="n">
-        <v>1140001</v>
+        <v>1140003</v>
       </c>
       <c r="C321" t="n">
         <v>1</v>
       </c>
       <c r="D321" t="n">
-        <v>1140102</v>
+        <v>1140142</v>
       </c>
     </row>
     <row r="322">
       <c r="B322" t="n">
-        <v>1140002</v>
+        <v>1140003</v>
       </c>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D322" t="n">
-        <v>1140122</v>
+        <v>1140143</v>
       </c>
     </row>
     <row r="323">
       <c r="B323" t="n">
-        <v>1140002</v>
+        <v>1140003</v>
       </c>
       <c r="C323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D323" t="n">
-        <v>1140123</v>
+        <v>1140144</v>
       </c>
     </row>
     <row r="324">
       <c r="B324" t="n">
-        <v>1140002</v>
+        <v>1140003</v>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D324" t="n">
-        <v>1140124</v>
+        <v>1140145</v>
       </c>
     </row>
     <row r="325">
       <c r="B325" t="n">
-        <v>1140002</v>
+        <v>1140004</v>
       </c>
       <c r="C325" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>1140125</v>
+        <v>1140162</v>
       </c>
     </row>
     <row r="326">
       <c r="B326" t="n">
-        <v>1140003</v>
+        <v>1140004</v>
       </c>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D326" t="n">
-        <v>1140142</v>
+        <v>1140163</v>
       </c>
     </row>
     <row r="327">
       <c r="B327" t="n">
-        <v>1140003</v>
+        <v>1140004</v>
       </c>
       <c r="C327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D327" t="n">
-        <v>1140143</v>
+        <v>1140164</v>
       </c>
     </row>
     <row r="328">
       <c r="B328" t="n">
-        <v>1140003</v>
+        <v>1140004</v>
       </c>
       <c r="C328" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D328" t="n">
-        <v>1140144</v>
+        <v>1140165</v>
       </c>
     </row>
     <row r="329">
       <c r="B329" t="n">
-        <v>1140003</v>
+        <v>1140005</v>
       </c>
       <c r="C329" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>1140145</v>
+        <v>1140182</v>
       </c>
     </row>
     <row r="330">
       <c r="B330" t="n">
-        <v>1140004</v>
+        <v>1140005</v>
       </c>
       <c r="C330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D330" t="n">
-        <v>1140162</v>
+        <v>1140183</v>
       </c>
     </row>
     <row r="331">
       <c r="B331" t="n">
-        <v>1140004</v>
+        <v>1140005</v>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D331" t="n">
-        <v>1140163</v>
+        <v>1140184</v>
       </c>
     </row>
     <row r="332">
       <c r="B332" t="n">
-        <v>1140004</v>
+        <v>1140005</v>
       </c>
       <c r="C332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D332" t="n">
-        <v>1140164</v>
+        <v>1140185</v>
       </c>
     </row>
     <row r="333">
       <c r="B333" t="n">
-        <v>1140004</v>
+        <v>1140006</v>
       </c>
       <c r="C333" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D333" t="n">
-        <v>1140165</v>
+        <v>1140202</v>
       </c>
     </row>
     <row r="334">
       <c r="B334" t="n">
-        <v>1140005</v>
+        <v>1140006</v>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D334" t="n">
-        <v>1140182</v>
+        <v>1140203</v>
       </c>
     </row>
     <row r="335">
       <c r="B335" t="n">
-        <v>1140005</v>
+        <v>1140006</v>
       </c>
       <c r="C335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D335" t="n">
-        <v>1140183</v>
+        <v>1140204</v>
       </c>
     </row>
     <row r="336">
       <c r="B336" t="n">
-        <v>1140005</v>
+        <v>1140006</v>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D336" t="n">
-        <v>1140184</v>
+        <v>1140205</v>
       </c>
     </row>
     <row r="337">
       <c r="B337" t="n">
-        <v>1140005</v>
+        <v>1140007</v>
       </c>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D337" t="n">
-        <v>1140185</v>
+        <v>1140222</v>
       </c>
     </row>
     <row r="338">
       <c r="B338" t="n">
-        <v>1140006</v>
+        <v>1140007</v>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D338" t="n">
-        <v>1140202</v>
+        <v>1140223</v>
       </c>
     </row>
     <row r="339">
       <c r="B339" t="n">
-        <v>1140006</v>
+        <v>1140007</v>
       </c>
       <c r="C339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D339" t="n">
-        <v>1140203</v>
+        <v>1140224</v>
       </c>
     </row>
     <row r="340">
       <c r="B340" t="n">
-        <v>1140006</v>
+        <v>1140007</v>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D340" t="n">
-        <v>1140204</v>
+        <v>1140225</v>
       </c>
     </row>
     <row r="341">
       <c r="B341" t="n">
-        <v>1140006</v>
+        <v>1140008</v>
       </c>
       <c r="C341" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>1140205</v>
+        <v>1140242</v>
       </c>
     </row>
     <row r="342">
       <c r="B342" t="n">
-        <v>1140007</v>
+        <v>1140008</v>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D342" t="n">
-        <v>1140222</v>
+        <v>1140243</v>
       </c>
     </row>
     <row r="343">
       <c r="B343" t="n">
-        <v>1140007</v>
+        <v>1140009</v>
       </c>
       <c r="C343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D343" t="n">
-        <v>1140223</v>
+        <v>1140262</v>
       </c>
     </row>
     <row r="344">
       <c r="B344" t="n">
-        <v>1140007</v>
+        <v>1140009</v>
       </c>
       <c r="C344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D344" t="n">
-        <v>1140224</v>
+        <v>1140263</v>
       </c>
     </row>
     <row r="345">
       <c r="B345" t="n">
-        <v>1140007</v>
+        <v>1140010</v>
       </c>
       <c r="C345" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D345" t="n">
-        <v>1140225</v>
+        <v>1140282</v>
       </c>
     </row>
     <row r="346">
       <c r="B346" t="n">
-        <v>1140008</v>
+        <v>1140010</v>
       </c>
       <c r="C346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D346" t="n">
-        <v>1140242</v>
+        <v>1140283</v>
       </c>
     </row>
     <row r="347">
       <c r="B347" t="n">
-        <v>1140008</v>
+        <v>110</v>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D347" t="n">
-        <v>1140243</v>
+        <v>1140302</v>
       </c>
     </row>
     <row r="348">
       <c r="B348" t="n">
-        <v>1140009</v>
+        <v>110</v>
       </c>
       <c r="C348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D348" t="n">
-        <v>1140262</v>
+        <v>1140303</v>
       </c>
     </row>
     <row r="349">
       <c r="B349" t="n">
-        <v>1140009</v>
+        <v>1140012</v>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D349" t="n">
-        <v>1140263</v>
+        <v>1140322</v>
       </c>
     </row>
     <row r="350">
       <c r="B350" t="n">
-        <v>1140010</v>
+        <v>1140012</v>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D350" t="n">
-        <v>1140282</v>
+        <v>1140323</v>
       </c>
     </row>
     <row r="351">
       <c r="B351" t="n">
-        <v>1140010</v>
+        <v>1140012</v>
       </c>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D351" t="n">
-        <v>1140283</v>
+        <v>1140324</v>
       </c>
     </row>
     <row r="352">
       <c r="B352" t="n">
-        <v>110</v>
+        <v>1140012</v>
       </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D352" t="n">
-        <v>1140302</v>
+        <v>1140325</v>
       </c>
     </row>
     <row r="353">
       <c r="B353" t="n">
-        <v>110</v>
+        <v>1140012</v>
       </c>
       <c r="C353" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D353" t="n">
-        <v>1140303</v>
+        <v>1140326</v>
       </c>
     </row>
     <row r="354">
       <c r="B354" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C354" t="n">
         <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>1140322</v>
+        <v>1150102</v>
       </c>
     </row>
     <row r="355">
       <c r="B355" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C355" t="n">
         <v>2</v>
       </c>
       <c r="D355" t="n">
-        <v>1140323</v>
+        <v>1150103</v>
       </c>
     </row>
     <row r="356">
       <c r="B356" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C356" t="n">
         <v>3</v>
       </c>
       <c r="D356" t="n">
-        <v>1140324</v>
+        <v>1150104</v>
       </c>
     </row>
     <row r="357">
       <c r="B357" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C357" t="n">
         <v>4</v>
       </c>
       <c r="D357" t="n">
-        <v>1140325</v>
+        <v>1150105</v>
       </c>
     </row>
     <row r="358">
       <c r="B358" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C358" t="n">
         <v>5</v>
       </c>
       <c r="D358" t="n">
-        <v>1140326</v>
+        <v>1150106</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1150122</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1150142</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariantAbility.xlsx
+++ b/config/data/EnemyVariantAbility.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,123 +571,123 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>11025</v>
+        <v>11027</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>11023</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>11024</v>
+        <v>11038</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>11022</v>
+        <v>11033</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11026</v>
+        <v>11039</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11027</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>11028</v>
+        <v>11046</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>11030</v>
+        <v>11037</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>11029</v>
+        <v>11041</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>11031</v>
+        <v>11043</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>11032</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="19">
@@ -695,10 +695,10 @@
         <v>105</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>11038</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         <v>105</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>11033</v>
+        <v>11044</v>
       </c>
     </row>
     <row r="21">
@@ -717,10 +717,10 @@
         <v>105</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>11039</v>
+        <v>11045</v>
       </c>
     </row>
     <row r="22">
@@ -728,10 +728,10 @@
         <v>105</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>11040</v>
+        <v>11042</v>
       </c>
     </row>
     <row r="23">
@@ -739,527 +739,3717 @@
         <v>105</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>11046</v>
+        <v>11036</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11037</v>
+        <v>11055</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>11041</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11043</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>11034</v>
+        <v>11019</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>11035</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>11044</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>11045</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>11042</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>11036</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>11047</v>
+        <v>11015</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>11048</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>107</v>
+        <v>980001</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>11050</v>
+        <v>980101</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>107</v>
+        <v>980001</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>11049</v>
+        <v>980102</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>108</v>
+        <v>980001</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>11052</v>
+        <v>980103</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>108</v>
+        <v>980001</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>11053</v>
+        <v>980104</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>108</v>
+        <v>980001</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>11051</v>
+        <v>980105</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>109</v>
+        <v>980001</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>11055</v>
+        <v>980106</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>109</v>
+        <v>980001</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>11054</v>
+        <v>980107</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>11057</v>
+        <v>980108</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>11058</v>
+        <v>980109</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>11056</v>
+        <v>980110</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>11062</v>
+        <v>980111</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>11060</v>
+        <v>980112</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>11063</v>
+        <v>980113</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>11061</v>
+        <v>980114</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>11059</v>
+        <v>990101</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>95</v>
+        <v>990001</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>11001</v>
+        <v>990102</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>95</v>
+        <v>990001</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>11002</v>
+        <v>990103</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>96</v>
+        <v>990001</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>11005</v>
+        <v>990104</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>96</v>
+        <v>990001</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>11003</v>
+        <v>990105</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>96</v>
+        <v>990001</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>11006</v>
+        <v>990106</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>96</v>
+        <v>990001</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>11004</v>
+        <v>990107</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>97</v>
+        <v>990001</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>11008</v>
+        <v>990108</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>97</v>
+        <v>1000001</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>11011</v>
+        <v>1000101</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>97</v>
+        <v>1000001</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>11009</v>
+        <v>1000102</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>97</v>
+        <v>1000001</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>11007</v>
+        <v>1000103</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>97</v>
+        <v>1000001</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>11010</v>
+        <v>1000104</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>11012</v>
+        <v>1000105</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>11019</v>
+        <v>1000106</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>11017</v>
+        <v>1000109</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>98</v>
+        <v>1010001</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>11016</v>
+        <v>1010101</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>98</v>
+        <v>1010001</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>11014</v>
+        <v>1010102</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>98</v>
+        <v>1010001</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>11020</v>
+        <v>1010103</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>98</v>
+        <v>1010001</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>11018</v>
+        <v>1010104</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>98</v>
+        <v>1020001</v>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>11015</v>
+        <v>1020101</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>98</v>
+        <v>1020001</v>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>11013</v>
+        <v>1020102</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1020103</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1020104</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1020105</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1020106</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1020107</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1020108</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1020109</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1030101</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1030102</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1030103</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1030104</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1030105</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C82" t="n">
+        <v>6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1030106</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1030108</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1030109</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1040101</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1040102</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1040103</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1040104</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1040105</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1040106</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1040107</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1040108</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C93" t="n">
+        <v>9</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1040112</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1040113</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1050101</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1050102</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1050103</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1050104</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1060101</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1060102</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1060103</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1060104</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1060105</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C104" t="n">
+        <v>6</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1060106</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C105" t="n">
+        <v>7</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1060107</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1060108</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C107" t="n">
+        <v>9</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1060109</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1070101</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C109" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1070102</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1070103</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1070104</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C112" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1070105</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C113" t="n">
+        <v>6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1070106</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1070107</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C115" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1070108</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C116" t="n">
+        <v>9</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1070109</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C117" t="n">
+        <v>10</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1070110</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1080101</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1080102</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1080103</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1080104</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1080105</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C123" t="n">
+        <v>6</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1080106</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C124" t="n">
+        <v>7</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1080107</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>95</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1090102</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>95</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1090103</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1090122</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1090123</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1090124</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1090142</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1090143</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1090144</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1090162</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1090163</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1090182</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1090202</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1090203</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1090204</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>96</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1090222</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>96</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1090223</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>96</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1090224</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>96</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1090225</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1090242</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1090243</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1090244</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C146" t="n">
+        <v>4</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1090245</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1090262</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1090282</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1090283</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1090284</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C151" t="n">
+        <v>4</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1090285</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1090302</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1090303</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1090304</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C155" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1090305</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C156" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1090306</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1090322</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1090323</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>97</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1100102</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>97</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1100103</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>97</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1100104</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>97</v>
+      </c>
+      <c r="C162" t="n">
+        <v>4</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1100105</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1100122</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1100142</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1100143</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1100162</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1100163</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1100164</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C169" t="n">
+        <v>4</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1100165</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
         <v>99</v>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="n">
-        <v>11021</v>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1100182</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1100202</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1100203</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1100204</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1100222</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1100223</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1100224</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C177" t="n">
+        <v>4</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1100225</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>100</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1100242</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>100</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1100243</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>100</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1100244</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>100</v>
+      </c>
+      <c r="C181" t="n">
+        <v>4</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1100245</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1100262</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1100263</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1100264</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1100265</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1100266</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1100282</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1100283</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1100284</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C190" t="n">
+        <v>4</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1100285</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1100286</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1100302</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1100322</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1100323</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1100324</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1110102</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1110103</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1110104</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1110105</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1110122</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1110142</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1110143</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1110144</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C204" t="n">
+        <v>4</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1110145</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1110162</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C206" t="n">
+        <v>2</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1110163</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1110164</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C208" t="n">
+        <v>4</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1110165</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1110182</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C210" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1110183</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1110184</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1110202</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>102</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1110222</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>102</v>
+      </c>
+      <c r="C214" t="n">
+        <v>2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1110223</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1110242</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1110262</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>103</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1110282</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1110302</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C219" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1110303</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1110304</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1110305</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C222" t="n">
+        <v>5</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1110306</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>104</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1110322</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1120102</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C225" t="n">
+        <v>2</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1120103</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1120122</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C227" t="n">
+        <v>2</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1120123</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1120142</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1120143</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1120144</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1120145</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C232" t="n">
+        <v>5</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1120146</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C233" t="n">
+        <v>6</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1120147</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C234" t="n">
+        <v>7</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1120148</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1120162</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1120163</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1120164</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1120165</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>106</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1120182</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1120202</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1120203</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1120204</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1120205</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1120222</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C245" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1120223</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1120224</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C247" t="n">
+        <v>4</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1120225</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>107</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1120242</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>107</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1120243</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>108</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1120262</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>108</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1120263</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>108</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1120264</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1120282</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C254" t="n">
+        <v>2</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1120283</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1120284</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1120302</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1120322</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C258" t="n">
+        <v>2</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1120323</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="n">
+        <v>1130102</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C260" t="n">
+        <v>2</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1130103</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1130104</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C262" t="n">
+        <v>4</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1130105</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C263" t="n">
+        <v>5</v>
+      </c>
+      <c r="D263" t="n">
+        <v>1130106</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1130122</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C265" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1130123</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1130142</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C267" t="n">
+        <v>2</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1130143</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1130144</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C269" t="n">
+        <v>4</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1130145</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C270" t="n">
+        <v>5</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1130146</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1130162</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C272" t="n">
+        <v>2</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1130163</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1130164</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C274" t="n">
+        <v>4</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1130165</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C275" t="n">
+        <v>5</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1130166</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C276" t="n">
+        <v>6</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1130167</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C277" t="n">
+        <v>7</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1130168</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C278" t="n">
+        <v>8</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1130169</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1130182</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C280" t="n">
+        <v>2</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1130183</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1130184</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C282" t="n">
+        <v>4</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1130185</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C283" t="n">
+        <v>5</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1130186</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C284" t="n">
+        <v>6</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1130187</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C285" t="n">
+        <v>7</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1130188</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1130202</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C287" t="n">
+        <v>2</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1130203</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1130204</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1130222</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1130242</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C291" t="n">
+        <v>2</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1130243</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1130244</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C293" t="n">
+        <v>4</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1130245</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C294" t="n">
+        <v>5</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1130246</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1130262</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1130282</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C297" t="n">
+        <v>2</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1130283</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C298" t="n">
+        <v>3</v>
+      </c>
+      <c r="D298" t="n">
+        <v>1130284</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C299" t="n">
+        <v>4</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1130285</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C300" t="n">
+        <v>5</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1130286</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C301" t="n">
+        <v>6</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1130287</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C302" t="n">
+        <v>7</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1130288</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C303" t="n">
+        <v>8</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1130289</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C304" t="n">
+        <v>9</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1130290</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1130302</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C306" t="n">
+        <v>2</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1130303</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1130304</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C308" t="n">
+        <v>4</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1130305</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C309" t="n">
+        <v>5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1130306</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C310" t="n">
+        <v>6</v>
+      </c>
+      <c r="D310" t="n">
+        <v>1130307</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1130322</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C312" t="n">
+        <v>2</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1130323</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C313" t="n">
+        <v>3</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1130324</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C314" t="n">
+        <v>4</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1130325</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C315" t="n">
+        <v>5</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1130326</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1140102</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1</v>
+      </c>
+      <c r="D317" t="n">
+        <v>1140122</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C318" t="n">
+        <v>2</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1140123</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1140124</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C320" t="n">
+        <v>4</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1140125</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" t="n">
+        <v>1140142</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C322" t="n">
+        <v>2</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1140143</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C323" t="n">
+        <v>3</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1140144</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C324" t="n">
+        <v>4</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1140145</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1140162</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C326" t="n">
+        <v>2</v>
+      </c>
+      <c r="D326" t="n">
+        <v>1140163</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3</v>
+      </c>
+      <c r="D327" t="n">
+        <v>1140164</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C328" t="n">
+        <v>4</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1140165</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1</v>
+      </c>
+      <c r="D329" t="n">
+        <v>1140182</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C330" t="n">
+        <v>2</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1140183</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C331" t="n">
+        <v>3</v>
+      </c>
+      <c r="D331" t="n">
+        <v>1140184</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C332" t="n">
+        <v>4</v>
+      </c>
+      <c r="D332" t="n">
+        <v>1140185</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1</v>
+      </c>
+      <c r="D333" t="n">
+        <v>1140202</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C334" t="n">
+        <v>2</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1140203</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C335" t="n">
+        <v>3</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1140204</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C336" t="n">
+        <v>4</v>
+      </c>
+      <c r="D336" t="n">
+        <v>1140205</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1</v>
+      </c>
+      <c r="D337" t="n">
+        <v>1140222</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C338" t="n">
+        <v>2</v>
+      </c>
+      <c r="D338" t="n">
+        <v>1140223</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C339" t="n">
+        <v>3</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1140224</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C340" t="n">
+        <v>4</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1140225</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1</v>
+      </c>
+      <c r="D341" t="n">
+        <v>1140242</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C342" t="n">
+        <v>2</v>
+      </c>
+      <c r="D342" t="n">
+        <v>1140243</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C343" t="n">
+        <v>1</v>
+      </c>
+      <c r="D343" t="n">
+        <v>1140262</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C344" t="n">
+        <v>2</v>
+      </c>
+      <c r="D344" t="n">
+        <v>1140263</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+      <c r="D345" t="n">
+        <v>1140282</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C346" t="n">
+        <v>2</v>
+      </c>
+      <c r="D346" t="n">
+        <v>1140283</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>110</v>
+      </c>
+      <c r="C347" t="n">
+        <v>1</v>
+      </c>
+      <c r="D347" t="n">
+        <v>1140302</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>110</v>
+      </c>
+      <c r="C348" t="n">
+        <v>2</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1140303</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1</v>
+      </c>
+      <c r="D349" t="n">
+        <v>1140322</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C350" t="n">
+        <v>2</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1140323</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C351" t="n">
+        <v>3</v>
+      </c>
+      <c r="D351" t="n">
+        <v>1140324</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C352" t="n">
+        <v>4</v>
+      </c>
+      <c r="D352" t="n">
+        <v>1140325</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C353" t="n">
+        <v>5</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1140326</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>111</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1150102</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>111</v>
+      </c>
+      <c r="C355" t="n">
+        <v>2</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1150103</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>111</v>
+      </c>
+      <c r="C356" t="n">
+        <v>3</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1150104</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>111</v>
+      </c>
+      <c r="C357" t="n">
+        <v>4</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1150105</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>111</v>
+      </c>
+      <c r="C358" t="n">
+        <v>5</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1150106</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1150122</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1150142</v>
       </c>
     </row>
   </sheetData>
